--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>69,262 €</t>
+          <t>71,124 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>72.9%</t>
+          <t>74.9%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>25,160 €</t>
+          <t>27,022 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>586 h</t>
+          <t>599 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>72.8%</t>
+          <t>74.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -1761,7 +1761,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="15" t="n">
-        <v>12.25</v>
+        <v>16.25</v>
       </c>
       <c r="L14" s="15" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         <v>1978</v>
       </c>
       <c r="O14" s="16" t="n">
-        <v>1978</v>
+        <v>2451</v>
       </c>
       <c r="P14" s="16" t="n">
-        <v>161.47</v>
+        <v>150.83</v>
       </c>
     </row>
     <row r="15">
@@ -7693,7 +7693,7 @@
         <v>5</v>
       </c>
       <c r="K97" s="12" t="n">
-        <v>2.5</v>
+        <v>5.5</v>
       </c>
       <c r="L97" s="12" t="inlineStr">
         <is>
@@ -7709,10 +7709,10 @@
         <v>1500</v>
       </c>
       <c r="O97" s="17" t="n">
-        <v>322.35</v>
+        <v>752.15</v>
       </c>
       <c r="P97" s="13" t="n">
-        <v>128.94</v>
+        <v>136.75</v>
       </c>
     </row>
     <row r="98">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="G116" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H116" s="15" t="inlineStr">
@@ -10611,10 +10611,10 @@
         <v>2323</v>
       </c>
       <c r="O138" s="17" t="n">
-        <v>0</v>
+        <v>832.374</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>0</v>
+        <v>138.73</v>
       </c>
     </row>
     <row r="139">
@@ -10891,10 +10891,10 @@
         <v>0</v>
       </c>
       <c r="O142" s="16" t="n">
-        <v>0</v>
+        <v>126.2</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>0</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="143">
@@ -11501,7 +11501,7 @@
         <v>15</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>6.5</v>
+        <v>6.75</v>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H155" s="12" t="inlineStr"/>
@@ -13206,7 +13206,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr"/>
@@ -14119,10 +14119,10 @@
         <v>57707.2</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>69262.265</v>
+        <v>71123.63900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>193.6</v>
+        <v>194.85</v>
       </c>
     </row>
   </sheetData>
@@ -15343,26 +15343,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>205.75</v>
+        <v>209.75</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>36.25</v>
+        <v>39.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>247.75</v>
+        <v>255</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>69.5</v>
+        <v>74</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>455.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>56.0%</t>
         </is>
       </c>
     </row>
@@ -15373,10 +15373,10 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>101</v>
+        <v>96.5</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>6.25</v>
+        <v>10.75</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>2.25</v>
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>135.08</v>
+        <v>136.33</v>
       </c>
     </row>
   </sheetData>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>380590</v>
+        <v>378728</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>131204</v>
+        <v>129343</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>249385</v>
@@ -15514,10 +15514,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>175495</v>
+        <v>173633</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>68195</v>
+        <v>66334</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>107300</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>71,124 €</t>
+          <t>71,407 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>74.9%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44,102 €</t>
+          <t>44,385 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>258</t>
+          <t>257</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -4553,10 +4553,10 @@
         <v>1416</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>849.6</v>
+        <v>1132.8</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>485.49</v>
+        <v>647.3099999999999</v>
       </c>
     </row>
     <row r="54">
@@ -14119,10 +14119,10 @@
         <v>57707.2</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>71123.63900000001</v>
+        <v>71406.83900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>194.85</v>
+        <v>195.63</v>
       </c>
     </row>
   </sheetData>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>378728</v>
+        <v>378445</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>129343</v>
+        <v>129059</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>249385</v>
@@ -15539,10 +15539,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>205095</v>
+        <v>204811</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>63009</v>
+        <v>62726</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>142086</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -898,7 +898,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -16437,7 +16437,11 @@
       </c>
       <c r="F22" s="12" t="inlineStr"/>
       <c r="G22" s="12" t="inlineStr"/>
-      <c r="H22" s="12" t="inlineStr"/>
+      <c r="H22" s="12" t="inlineStr">
+        <is>
+          <t>00172868</t>
+        </is>
+      </c>
       <c r="I22" s="27" t="n">
         <v>500</v>
       </c>
@@ -16651,7 +16655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F26"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -16672,7 +16676,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>19 clôture(s) : 16 projet(s), 3 rework</t>
+          <t>20 clôture(s) : 17 projet(s), 3 rework</t>
         </is>
       </c>
     </row>
@@ -16892,17 +16896,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLA</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -16922,17 +16926,17 @@
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLA</t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -16946,23 +16950,23 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP -</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -16976,28 +16980,28 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Lit</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP -</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -17006,23 +17010,23 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Lit</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
@@ -17036,23 +17040,23 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-26825</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -17066,23 +17070,23 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-26825</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -17096,23 +17100,23 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -17126,23 +17130,23 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -17156,23 +17160,23 @@
         </is>
       </c>
       <c r="F19" s="15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -17190,49 +17194,49 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-5596</t>
-        </is>
-      </c>
-      <c r="B21" s="28" t="inlineStr">
-        <is>
-          <t>[IVRY-SUR-SEINE - GEODP TLPE/Voirie/Terrasse] GEODP V2</t>
-        </is>
-      </c>
-      <c r="C21" s="28" t="inlineStr">
-        <is>
-          <t>IVRY-SUR-SEINE</t>
-        </is>
-      </c>
-      <c r="D21" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E21" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F21" s="28" t="n">
-        <v>34</v>
+      <c r="A21" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33804</t>
+        </is>
+      </c>
+      <c r="B21" s="15" t="inlineStr">
+        <is>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="D21" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-6161</t>
+          <t>PDMDEP-5596</t>
         </is>
       </c>
       <c r="B22" s="28" t="inlineStr">
         <is>
-          <t>[VILLEURBANNE] GEODP V2</t>
+          <t>[IVRY-SUR-SEINE - GEODP TLPE/Voirie/Terrasse] GEODP V2</t>
         </is>
       </c>
       <c r="C22" s="28" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>IVRY-SUR-SEINE</t>
         </is>
       </c>
       <c r="D22" s="28" t="inlineStr">
@@ -17252,59 +17256,89 @@
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-6161</t>
+        </is>
+      </c>
+      <c r="B23" s="28" t="inlineStr">
+        <is>
+          <t>[VILLEURBANNE] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C23" s="28" t="inlineStr">
+        <is>
+          <t>VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="D23" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E23" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F23" s="28" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-16116</t>
         </is>
       </c>
-      <c r="B23" s="28" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AM</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C24" s="28" t="inlineStr">
         <is>
           <t>CD 01</t>
         </is>
       </c>
-      <c r="D23" s="28" t="inlineStr">
+      <c r="D24" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E23" s="28" t="inlineStr">
+      <c r="E24" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F23" s="28" t="n">
+      <c r="F24" s="28" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="24"/>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B25" s="18" t="n"/>
-      <c r="C25" s="18" t="n"/>
-      <c r="D25" s="18" t="n"/>
-      <c r="E25" s="18" t="n"/>
-      <c r="F25" s="18" t="n">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="29" t="inlineStr">
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="18" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B26" s="29" t="n"/>
-      <c r="C26" s="29" t="n"/>
-      <c r="D26" s="29" t="n"/>
-      <c r="E26" s="29" t="n"/>
-      <c r="F26" s="29" t="n">
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="29" t="n"/>
+      <c r="F27" s="29" t="n">
         <v>3</v>
       </c>
     </row>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>71,407 €</t>
+          <t>73,699 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>77.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>44,385 €</t>
+          <t>46,678 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>599 h</t>
+          <t>606 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>74.4%</t>
+          <t>75.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -898,7 +898,7 @@
     <row r="25" ht="26" customHeight="1">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B25" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>257</t>
+          <t>255</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -6126,10 +6126,10 @@
         </is>
       </c>
       <c r="N75" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O75" s="13" t="n">
         <v>283.5</v>
-      </c>
-      <c r="O75" s="17" t="n">
-        <v>0</v>
       </c>
       <c r="P75" s="13" t="n">
         <v>0</v>
@@ -8346,10 +8346,10 @@
         </is>
       </c>
       <c r="N106" s="16" t="n">
-        <v>1000</v>
-      </c>
-      <c r="O106" s="17" t="n">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="O106" s="16" t="n">
+        <v>2009</v>
       </c>
       <c r="P106" s="16" t="n">
         <v>0</v>
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
@@ -14116,13 +14116,13 @@
       <c r="L193" s="18" t="inlineStr"/>
       <c r="M193" s="18" t="inlineStr"/>
       <c r="N193" s="19" t="n">
-        <v>57707.2</v>
+        <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>71406.83900000001</v>
+        <v>73699.33900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>195.63</v>
+        <v>201.08</v>
       </c>
     </row>
   </sheetData>
@@ -15343,7 +15343,7 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>209.75</v>
+        <v>211.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>39.5</v>
@@ -15352,17 +15352,17 @@
         <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>255</v>
+        <v>256.5</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>74</v>
+        <v>76.5</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>455.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>136.33</v>
+        <v>138.83</v>
       </c>
     </row>
   </sheetData>
@@ -15489,16 +15489,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>378445</v>
+        <v>376152</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>129059</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>249385</v>
+        <v>247093</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>157314</v>
+        <v>155021</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>22749</v>
@@ -15539,16 +15539,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>204811</v>
+        <v>202519</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>62726</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>142086</v>
+        <v>139793</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>68510</v>
+        <v>66218</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>10557</v>
@@ -16655,7 +16655,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -16676,7 +16676,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20 clôture(s) : 17 projet(s), 3 rework</t>
+          <t>21 clôture(s) : 18 projet(s), 3 rework</t>
         </is>
       </c>
     </row>
@@ -16836,17 +16836,17 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-31938</t>
+          <t>PDMDEP-30358</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">METROPOLE TOULON- GeODP tous modules - intégration en masse </t>
+          <t>[COMMUNE D'ARGELES-SUR-MER] - Migration V2 classique</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>COMMUNE D'ARGELES-SUR-MER</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
@@ -16860,23 +16860,23 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32331</t>
+          <t>PDMDEP-31938</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
+          <t xml:space="preserve">METROPOLE TOULON- GeODP tous modules - intégration en masse </t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
@@ -16896,17 +16896,17 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32703</t>
+          <t>PDMDEP-32331</t>
         </is>
       </c>
       <c r="B11" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
+          <t xml:space="preserve">[COMMUNE DE CHALONS EN CHAMPAGNE] - Migration GEODP Placier </t>
         </is>
       </c>
       <c r="C11" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MIRIBEL</t>
+          <t>COMMUNE DE CHALONS EN CHAMPAGNE</t>
         </is>
       </c>
       <c r="D11" s="15" t="inlineStr">
@@ -16920,23 +16920,23 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32860</t>
+          <t>PDMDEP-32703</t>
         </is>
       </c>
       <c r="B12" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLA</t>
+          <t xml:space="preserve">[MAIRIE DE MIRIBEL] - MIGRATION PLACIER SIMPLE + PAX </t>
         </is>
       </c>
       <c r="C12" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LE LUC EN PROVENCE</t>
+          <t>MAIRIE DE MIRIBEL</t>
         </is>
       </c>
       <c r="D12" s="12" t="inlineStr">
@@ -16956,17 +16956,17 @@
     <row r="13">
       <c r="A13" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33239</t>
+          <t>PDMDEP-32860</t>
         </is>
       </c>
       <c r="B13" s="15" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V</t>
+          <t>[COMMUNE DE LE LUC EN PROVENCE] - MIGRATION SIMPLE GEODP PLA</t>
         </is>
       </c>
       <c r="C13" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE LODEVE</t>
+          <t>COMMUNE DE LE LUC EN PROVENCE</t>
         </is>
       </c>
       <c r="D13" s="15" t="inlineStr">
@@ -16980,23 +16980,23 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33553</t>
+          <t>PDMDEP-33239</t>
         </is>
       </c>
       <c r="B14" s="12" t="inlineStr">
         <is>
-          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP -</t>
+          <t>[MAIRIE DE LODEVE] - Migracier activité Placier vers Geodp V</t>
         </is>
       </c>
       <c r="C14" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>MAIRIE DE LODEVE</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -17010,28 +17010,28 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-33553</t>
         </is>
       </c>
       <c r="B15" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Lit</t>
+          <t>[METROPOLE TOULON-PROVENCE-MEDITERRANEE] - MM - Up - GeODP -</t>
         </is>
       </c>
       <c r="C15" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="E15" s="15" t="inlineStr">
@@ -17040,23 +17040,23 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B16" s="12" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Lit</t>
         </is>
       </c>
       <c r="C16" s="12" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="D16" s="12" t="inlineStr">
@@ -17070,23 +17070,23 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-26825</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B17" s="15" t="inlineStr">
         <is>
-          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
         </is>
       </c>
       <c r="C17" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE COLOMBES - DSIO</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="D17" s="15" t="inlineStr">
@@ -17100,23 +17100,23 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-31947</t>
+          <t>PDMDEP-26825</t>
         </is>
       </c>
       <c r="B18" s="12" t="inlineStr">
         <is>
-          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
+          <t>[COLOMBES] - Litteralis Vision &amp; Publi</t>
         </is>
       </c>
       <c r="C18" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
+          <t>VILLE DE COLOMBES - DSIO</t>
         </is>
       </c>
       <c r="D18" s="12" t="inlineStr">
@@ -17130,23 +17130,23 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-32552</t>
+          <t>PDMDEP-31947</t>
         </is>
       </c>
       <c r="B19" s="15" t="inlineStr">
         <is>
-          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage</t>
+          <t>[DEPARTEMENT DE LA MOSELLE (CD 57)] - SSO/LDAP</t>
         </is>
       </c>
       <c r="C19" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE CHALON SUR SAONE</t>
+          <t>DEPARTEMENT DE LA MOSELLE (CD 57)</t>
         </is>
       </c>
       <c r="D19" s="15" t="inlineStr">
@@ -17160,23 +17160,23 @@
         </is>
       </c>
       <c r="F19" s="15" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33720</t>
+          <t>PDMDEP-32552</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
+          <t>[CHALON SUR SAONE] - Littéralis - Intégration et paramétrage</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE LEVALLOIS PERRET</t>
+          <t>VILLE DE CHALON SUR SAONE</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
@@ -17190,23 +17190,23 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33804</t>
+          <t>PDMDEP-33720</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>[CD 73)] - Purge arrêtés temporaires</t>
+          <t>[COMMUNE DE LEVALLOIS PERRET] - PRESTA PURGE DES ACTES EN UR</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+          <t>COMMUNE DE LEVALLOIS PERRET</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
@@ -17224,49 +17224,49 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="28" t="inlineStr">
-        <is>
-          <t>PDMDEP-5596</t>
-        </is>
-      </c>
-      <c r="B22" s="28" t="inlineStr">
-        <is>
-          <t>[IVRY-SUR-SEINE - GEODP TLPE/Voirie/Terrasse] GEODP V2</t>
-        </is>
-      </c>
-      <c r="C22" s="28" t="inlineStr">
-        <is>
-          <t>IVRY-SUR-SEINE</t>
-        </is>
-      </c>
-      <c r="D22" s="28" t="inlineStr">
-        <is>
-          <t>GEODP</t>
-        </is>
-      </c>
-      <c r="E22" s="28" t="inlineStr">
-        <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="F22" s="28" t="n">
-        <v>34</v>
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33804</t>
+        </is>
+      </c>
+      <c r="B22" s="12" t="inlineStr">
+        <is>
+          <t>[CD 73)] - Purge arrêtés temporaires</t>
+        </is>
+      </c>
+      <c r="C22" s="12" t="inlineStr">
+        <is>
+          <t>CONSEIL DEPARTEMENTAL DE LA SAVOIE (CD 73)</t>
+        </is>
+      </c>
+      <c r="D22" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="E22" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="F22" s="12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="28" t="inlineStr">
         <is>
-          <t>PDMDEP-6161</t>
+          <t>PDMDEP-5596</t>
         </is>
       </c>
       <c r="B23" s="28" t="inlineStr">
         <is>
-          <t>[VILLEURBANNE] GEODP V2</t>
+          <t>[IVRY-SUR-SEINE - GEODP TLPE/Voirie/Terrasse] GEODP V2</t>
         </is>
       </c>
       <c r="C23" s="28" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>IVRY-SUR-SEINE</t>
         </is>
       </c>
       <c r="D23" s="28" t="inlineStr">
@@ -17286,59 +17286,89 @@
     <row r="24">
       <c r="A24" s="28" t="inlineStr">
         <is>
+          <t>PDMDEP-6161</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>[VILLEURBANNE] GEODP V2</t>
+        </is>
+      </c>
+      <c r="C24" s="28" t="inlineStr">
+        <is>
+          <t>VILLEURBANNE</t>
+        </is>
+      </c>
+      <c r="D24" s="28" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="E24" s="28" t="inlineStr">
+        <is>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="F24" s="28" t="n">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="28" t="inlineStr">
+        <is>
           <t>PDMDEP-16116</t>
         </is>
       </c>
-      <c r="B24" s="28" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>[CD 01] MV + réinstal serveur + flux + publi + TDC SIG et AM</t>
         </is>
       </c>
-      <c r="C24" s="28" t="inlineStr">
+      <c r="C25" s="28" t="inlineStr">
         <is>
           <t>CD 01</t>
         </is>
       </c>
-      <c r="D24" s="28" t="inlineStr">
+      <c r="D25" s="28" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
         </is>
       </c>
-      <c r="E24" s="28" t="inlineStr">
+      <c r="E25" s="28" t="inlineStr">
         <is>
           <t>Rework</t>
         </is>
       </c>
-      <c r="F24" s="28" t="n">
+      <c r="F25" s="28" t="n">
         <v>24</v>
       </c>
     </row>
-    <row r="25"/>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>TOTAL projets clôturés</t>
         </is>
       </c>
-      <c r="B26" s="18" t="n"/>
-      <c r="C26" s="18" t="n"/>
-      <c r="D26" s="18" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="18" t="n">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="29" t="inlineStr">
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="18" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="29" t="inlineStr">
         <is>
           <t>TOTAL rework clôturés</t>
         </is>
       </c>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
-      <c r="F27" s="29" t="n">
+      <c r="B28" s="29" t="n"/>
+      <c r="C28" s="29" t="n"/>
+      <c r="D28" s="29" t="n"/>
+      <c r="E28" s="29" t="n"/>
+      <c r="F28" s="29" t="n">
         <v>3</v>
       </c>
     </row>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>73,699 €</t>
+          <t>73,874 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>77.6%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,678 €</t>
+          <t>46,853 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>606 h</t>
+          <t>613 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>76.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -1705,10 +1705,10 @@
         <v>500</v>
       </c>
       <c r="O13" s="17" t="n">
-        <v>100</v>
+        <v>275</v>
       </c>
       <c r="P13" s="13" t="n">
-        <v>133.33</v>
+        <v>366.67</v>
       </c>
     </row>
     <row r="14">
@@ -2257,7 +2257,7 @@
         <v>1</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L21" s="12" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>2490</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>0</v>
+        <v>355.71</v>
       </c>
     </row>
     <row r="22">
@@ -14119,10 +14119,10 @@
         <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>73699.33900000001</v>
+        <v>73874.33900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>201.08</v>
+        <v>197.78</v>
       </c>
     </row>
   </sheetData>
@@ -15373,7 +15373,7 @@
         </is>
       </c>
       <c r="B6" s="12" t="n">
-        <v>96.5</v>
+        <v>103.5</v>
       </c>
       <c r="C6" s="12" t="n">
         <v>10.75</v>
@@ -15382,7 +15382,7 @@
         <v>2.25</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>109.5</v>
+        <v>116.5</v>
       </c>
       <c r="F6" s="12" t="n">
         <v>19.75</v>
@@ -15392,7 +15392,7 @@
       </c>
       <c r="H6" s="22" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>50.6%</t>
         </is>
       </c>
     </row>
@@ -15489,10 +15489,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>376152</v>
+        <v>375977</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>129059</v>
+        <v>128884</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>247093</v>
@@ -15539,10 +15539,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>202519</v>
+        <v>202344</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>62726</v>
+        <v>62551</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>139793</v>
@@ -15568,7 +15568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -15592,7 +15592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Épics créées ce mois — 21 commande(s)</t>
+          <t>Épics créées ce mois — 20 commande(s)</t>
         </is>
       </c>
     </row>
@@ -15692,22 +15692,22 @@
     <row r="6">
       <c r="A6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34466</t>
+          <t>PDMDEP-34825</t>
         </is>
       </c>
       <c r="B6" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34457</t>
+          <t>PDMDEP-34819</t>
         </is>
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Flèche</t>
+          <t>Ville de Bourges</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -15727,22 +15727,22 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>00172594</t>
+          <t>00177218</t>
         </is>
       </c>
       <c r="I6" s="27" t="n">
-        <v>4475</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34825</t>
+          <t>PDMDEP-34791</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34819</t>
+          <t>PDMDEP-34782</t>
         </is>
       </c>
       <c r="C7" s="15" t="inlineStr">
@@ -15752,7 +15752,7 @@
       </c>
       <c r="D7" s="15" t="inlineStr">
         <is>
-          <t>Ville de Bourges</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -15762,7 +15762,7 @@
       </c>
       <c r="F7" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="G7" s="15" t="inlineStr">
@@ -15772,32 +15772,32 @@
       </c>
       <c r="H7" s="15" t="inlineStr">
         <is>
-          <t>00177218</t>
+          <t>00177122</t>
         </is>
       </c>
       <c r="I7" s="26" t="n">
-        <v>0</v>
+        <v>2146.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34791</t>
+          <t>PDMDEP-34466</t>
         </is>
       </c>
       <c r="B8" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34782</t>
+          <t>PDMDEP-34457</t>
         </is>
       </c>
       <c r="C8" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>Commune de La Flèche</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -15807,7 +15807,7 @@
       </c>
       <c r="F8" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -15817,32 +15817,32 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>00177122</t>
+          <t>00172594</t>
         </is>
       </c>
       <c r="I8" s="27" t="n">
-        <v>2146.5</v>
+        <v>4475</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34481</t>
+          <t>PDMDEP-34768</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34475</t>
+          <t>PDMDEP-34761</t>
         </is>
       </c>
       <c r="C9" s="15" t="inlineStr">
         <is>
-          <t>06/07/2026</t>
+          <t>28/07/2026</t>
         </is>
       </c>
       <c r="D9" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Pontcharra</t>
+          <t>COMMUNE DU PUY EN VELAY</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -15862,32 +15862,32 @@
       </c>
       <c r="H9" s="15" t="inlineStr">
         <is>
-          <t>00172611</t>
+          <t>00177029</t>
         </is>
       </c>
       <c r="I9" s="26" t="n">
-        <v>1050</v>
+        <v>5585</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34768</t>
+          <t>PDMDEP-34481</t>
         </is>
       </c>
       <c r="B10" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34761</t>
+          <t>PDMDEP-34475</t>
         </is>
       </c>
       <c r="C10" s="12" t="inlineStr">
         <is>
-          <t>28/07/2026</t>
+          <t>06/07/2026</t>
         </is>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DU PUY EN VELAY</t>
+          <t>Mairie de Pontcharra</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -15907,11 +15907,11 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>00177029</t>
+          <t>00172611</t>
         </is>
       </c>
       <c r="I10" s="27" t="n">
-        <v>5585</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="11">
@@ -16322,22 +16322,22 @@
     <row r="20">
       <c r="A20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34499</t>
+          <t>PDMDEP-34861</t>
         </is>
       </c>
       <c r="B20" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34495</t>
+          <t>PDMDEP-34857</t>
         </is>
       </c>
       <c r="C20" s="12" t="inlineStr">
         <is>
-          <t>07/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CLICHY</t>
+          <t>COMMUNE DE BIARRITZ</t>
         </is>
       </c>
       <c r="E20" s="12" t="inlineStr">
@@ -16357,32 +16357,32 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>00172678</t>
+          <t>00177271</t>
         </is>
       </c>
       <c r="I20" s="27" t="n">
-        <v>4300</v>
+        <v>1700</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34861</t>
+          <t>PDMDEP-34722</t>
         </is>
       </c>
       <c r="B21" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34857</t>
+          <t>PDMDEP-34718</t>
         </is>
       </c>
       <c r="C21" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>24/07/2026</t>
         </is>
       </c>
       <c r="D21" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BIARRITZ</t>
+          <t>VILLE DE VILLEURBANNE</t>
         </is>
       </c>
       <c r="E21" s="15" t="inlineStr">
@@ -16402,11 +16402,11 @@
       </c>
       <c r="H21" s="15" t="inlineStr">
         <is>
-          <t>00177271</t>
+          <t>00176875</t>
         </is>
       </c>
       <c r="I21" s="26" t="n">
-        <v>1700</v>
+        <v>2800</v>
       </c>
     </row>
     <row r="22">
@@ -16449,22 +16449,22 @@
     <row r="23">
       <c r="A23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34852</t>
+          <t>PDMDEP-34499</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34848</t>
+          <t>PDMDEP-34495</t>
         </is>
       </c>
       <c r="C23" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>07/07/2026</t>
         </is>
       </c>
       <c r="D23" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRUAY LA BUISSIERE</t>
+          <t>COMMUNE DE CLICHY</t>
         </is>
       </c>
       <c r="E23" s="15" t="inlineStr">
@@ -16484,32 +16484,32 @@
       </c>
       <c r="H23" s="15" t="inlineStr">
         <is>
-          <t>00177232</t>
+          <t>00172678</t>
         </is>
       </c>
       <c r="I23" s="26" t="n">
-        <v>0</v>
+        <v>4300</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34722</t>
+          <t>PDMDEP-34654</t>
         </is>
       </c>
       <c r="B24" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34718</t>
+          <t>PDMDEP-34650</t>
         </is>
       </c>
       <c r="C24" s="12" t="inlineStr">
         <is>
-          <t>24/07/2026</t>
+          <t>21/07/2026</t>
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEURBANNE</t>
+          <t>DEPARTEMENT DE L AIN (CD 01)</t>
         </is>
       </c>
       <c r="E24" s="12" t="inlineStr">
@@ -16529,62 +16529,38 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>00176875</t>
+          <t>00176582</t>
         </is>
       </c>
       <c r="I24" s="27" t="n">
-        <v>2800</v>
+        <v>495</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34654</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34650</t>
-        </is>
-      </c>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>21/07/2026</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>DEPARTEMENT DE L AIN (CD 01)</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>LITTERALIS</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>Vente additionnelle</t>
-        </is>
-      </c>
-      <c r="G25" s="15" t="inlineStr">
-        <is>
-          <t>Services</t>
-        </is>
-      </c>
-      <c r="H25" s="15" t="inlineStr">
-        <is>
-          <t>00176582</t>
-        </is>
-      </c>
-      <c r="I25" s="26" t="n">
-        <v>495</v>
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>TOTAL</t>
+        </is>
+      </c>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="18" t="n"/>
+      <c r="G25" s="18" t="n"/>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>20 commande(s)</t>
+        </is>
+      </c>
+      <c r="I25" s="25" t="n">
+        <v>40484</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="inlineStr">
         <is>
-          <t>TOTAL</t>
+          <t>dont Littéralis</t>
         </is>
       </c>
       <c r="B26" s="18" t="n"/>
@@ -16595,17 +16571,17 @@
       <c r="G26" s="18" t="n"/>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>21 commande(s)</t>
+          <t>5 commande(s)</t>
         </is>
       </c>
       <c r="I26" s="25" t="n">
-        <v>40484</v>
+        <v>9795</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="inlineStr">
         <is>
-          <t>dont Littéralis</t>
+          <t>dont GEODP</t>
         </is>
       </c>
       <c r="B27" s="18" t="n"/>
@@ -16616,31 +16592,10 @@
       <c r="G27" s="18" t="n"/>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>6 commande(s)</t>
+          <t>15 commande(s)</t>
         </is>
       </c>
       <c r="I27" s="25" t="n">
-        <v>9795</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="inlineStr">
-        <is>
-          <t>dont GEODP</t>
-        </is>
-      </c>
-      <c r="B28" s="18" t="n"/>
-      <c r="C28" s="18" t="n"/>
-      <c r="D28" s="18" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="18" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="18" t="inlineStr">
-        <is>
-          <t>15 commande(s)</t>
-        </is>
-      </c>
-      <c r="I28" s="25" t="n">
         <v>30689</v>
       </c>
     </row>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>73,874 €</t>
+          <t>74,164 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>77.8%</t>
+          <t>78.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>46,853 €</t>
+          <t>47,143 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -4913,10 +4913,10 @@
         <v>0</v>
       </c>
       <c r="O58" s="16" t="n">
-        <v>203</v>
+        <v>493</v>
       </c>
       <c r="P58" s="16" t="n">
-        <v>81.2</v>
+        <v>197.2</v>
       </c>
     </row>
     <row r="59">
@@ -14119,10 +14119,10 @@
         <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>73874.33900000001</v>
+        <v>74164.33900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>197.78</v>
+        <v>198.56</v>
       </c>
     </row>
   </sheetData>
@@ -15489,16 +15489,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>375977</v>
+        <v>375687</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>128884</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>247093</v>
+        <v>246803</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>155021</v>
+        <v>154731</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>22749</v>
@@ -15539,16 +15539,16 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>202344</v>
+        <v>202054</v>
       </c>
       <c r="C7" s="27" t="n">
         <v>62551</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>139793</v>
+        <v>139503</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>66218</v>
+        <v>65928</v>
       </c>
       <c r="F7" s="27" t="n">
         <v>10557</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>613 h</t>
+          <t>630 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>78.2%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -912,7 +912,7 @@
       <c r="F25" s="7" t="n"/>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>256</t>
         </is>
       </c>
       <c r="H25" s="7" t="n"/>
@@ -928,7 +928,7 @@
     <row r="29" ht="26" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B29" s="7" t="n"/>
@@ -12756,7 +12756,7 @@
       </c>
       <c r="G170" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H170" s="15" t="inlineStr">
@@ -12773,7 +12773,7 @@
         <v>27</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L170" s="15" t="inlineStr">
         <is>
@@ -14122,7 +14122,7 @@
         <v>74164.33900000001</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>198.56</v>
+        <v>197.5</v>
       </c>
     </row>
   </sheetData>
@@ -15343,16 +15343,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>211.25</v>
+        <v>207.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>39.5</v>
+        <v>45.5</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>5.75</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>256.5</v>
+        <v>258.5</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>76.5</v>
@@ -15362,7 +15362,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
     </row>
@@ -15404,7 +15404,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>138.83</v>
+        <v>153.83</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -14327,7 +14327,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -14353,7 +14353,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tickets 'Matériel GEODP' clôturés ce mois — 8 ligne(s)</t>
+          <t>Tickets 'Matériel GEODP' clôturés ce mois — 9 ligne(s)</t>
         </is>
       </c>
     </row>
@@ -14736,22 +14736,22 @@
     <row r="11">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-32732</t>
+          <t>PDMDEP-33597</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+          <t>[Commune de Trets] - Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="C11" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE LA SENTINELLE</t>
+          <t>Commune de Trets</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Acquisition Geodp Caisse</t>
+          <t>Ajout d'un Module Caisse sur GEODP avec paiement CB</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -14766,7 +14766,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="H11" s="12" t="n">
@@ -14774,12 +14774,12 @@
       </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-32739</t>
+          <t>PDMDEP-33603</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>00163790</t>
+          <t>00168996</t>
         </is>
       </c>
       <c r="K11" s="13" t="n">
@@ -14789,73 +14789,126 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
+          <t>PDMDEP-32732</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="inlineStr">
+        <is>
+          <t>[MAIRIE DE LA SENTINELLE] - Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="C12" s="15" t="inlineStr">
+        <is>
+          <t>MAIRIE DE LA SENTINELLE</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="inlineStr">
+        <is>
+          <t>Acquisition Geodp Caisse</t>
+        </is>
+      </c>
+      <c r="E12" s="15" t="inlineStr">
+        <is>
+          <t>GEODP</t>
+        </is>
+      </c>
+      <c r="F12" s="15" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G12" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-32739</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="inlineStr">
+        <is>
+          <t>00163790</t>
+        </is>
+      </c>
+      <c r="K12" s="16" t="n">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
           <t>PDMDEP-32152</t>
         </is>
       </c>
-      <c r="B12" s="15" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">[COMMUNE DE CAVAILLON] - Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>COMMUNE DE CAVAILLON</t>
         </is>
       </c>
-      <c r="D12" s="15" t="inlineStr">
+      <c r="D13" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Migration GeODP Placier + CB + Formation sur site </t>
         </is>
       </c>
-      <c r="E12" s="15" t="inlineStr">
+      <c r="E13" s="12" t="inlineStr">
         <is>
           <t>GEODP</t>
         </is>
       </c>
-      <c r="F12" s="15" t="inlineStr">
-        <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="G12" s="15" t="inlineStr">
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="G13" s="12" t="inlineStr">
         <is>
           <t>Migration</t>
         </is>
       </c>
-      <c r="H12" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="15" t="inlineStr">
+      <c r="H13" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="12" t="inlineStr">
         <is>
           <t>PDMDEP-32159</t>
         </is>
       </c>
-      <c r="J12" s="15" t="inlineStr">
+      <c r="J13" s="12" t="inlineStr">
         <is>
           <t>00160662</t>
         </is>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K13" s="13" t="n">
         <v>1711.5</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="18" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B13" s="18" t="inlineStr"/>
-      <c r="C13" s="18" t="inlineStr"/>
-      <c r="D13" s="18" t="inlineStr"/>
-      <c r="E13" s="18" t="inlineStr"/>
-      <c r="F13" s="18" t="inlineStr"/>
-      <c r="G13" s="18" t="inlineStr"/>
-      <c r="H13" s="18" t="inlineStr"/>
-      <c r="I13" s="18" t="inlineStr"/>
-      <c r="J13" s="18" t="inlineStr"/>
-      <c r="K13" s="19" t="n">
-        <v>8231.5</v>
+      <c r="B14" s="18" t="inlineStr"/>
+      <c r="C14" s="18" t="inlineStr"/>
+      <c r="D14" s="18" t="inlineStr"/>
+      <c r="E14" s="18" t="inlineStr"/>
+      <c r="F14" s="18" t="inlineStr"/>
+      <c r="G14" s="18" t="inlineStr"/>
+      <c r="H14" s="18" t="inlineStr"/>
+      <c r="I14" s="18" t="inlineStr"/>
+      <c r="J14" s="18" t="inlineStr"/>
+      <c r="K14" s="19" t="n">
+        <v>9046.5</v>
       </c>
     </row>
   </sheetData>
@@ -14869,6 +14922,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A10" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A11" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A12" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A13" r:id="rId9"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>74,164 €</t>
+          <t>75,617 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>78.1%</t>
+          <t>79.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>47,143 €</t>
+          <t>48,595 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>630 h</t>
+          <t>631 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.2%</t>
+          <t>78.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -2273,10 +2273,10 @@
         <v>1660</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>2490</v>
+        <v>3942.5</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>355.71</v>
+        <v>563.21</v>
       </c>
     </row>
     <row r="22">
@@ -14119,10 +14119,10 @@
         <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>74164.33900000001</v>
+        <v>75616.83899999999</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>197.5</v>
+        <v>201.37</v>
       </c>
     </row>
   </sheetData>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>153.83</v>
+        <v>155.33</v>
       </c>
     </row>
   </sheetData>
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>375687</v>
+        <v>374235</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>128884</v>
+        <v>127432</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>246803</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>202054</v>
+        <v>200601</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>62551</v>
+        <v>61098</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>139503</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>75,617 €</t>
+          <t>75,672 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>79.6%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>27,022 €</t>
+          <t>27,077 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>631 h</t>
+          <t>639 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>78.4%</t>
+          <t>79.4%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -6257,7 +6257,7 @@
         <v>3</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="L77" s="12" t="inlineStr">
         <is>
@@ -6273,10 +6273,10 @@
         <v>0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>109.68</v>
+        <v>164.52</v>
       </c>
       <c r="P77" s="13" t="n">
-        <v>33.75</v>
+        <v>43.87</v>
       </c>
     </row>
     <row r="78">
@@ -11839,7 +11839,7 @@
         <v>16</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L156" s="15" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>1</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0.5</v>
+        <v>0.75</v>
       </c>
       <c r="L185" s="12" t="inlineStr"/>
       <c r="M185" s="12" t="inlineStr"/>
@@ -13807,7 +13807,7 @@
         <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>1.75</v>
+        <v>2.75</v>
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
@@ -13826,7 +13826,7 @@
         <v>680.8</v>
       </c>
       <c r="P187" s="13" t="n">
-        <v>389.03</v>
+        <v>247.56</v>
       </c>
     </row>
     <row r="188">
@@ -14119,10 +14119,10 @@
         <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>75616.83899999999</v>
+        <v>75671.679</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>201.37</v>
+        <v>200.32</v>
       </c>
     </row>
   </sheetData>
@@ -15397,26 +15397,26 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>207.25</v>
+        <v>209.25</v>
       </c>
       <c r="C5" s="15" t="n">
         <v>45.5</v>
       </c>
       <c r="D5" s="15" t="n">
-        <v>5.75</v>
+        <v>6</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>258.5</v>
+        <v>260.75</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>76.5</v>
+        <v>81</v>
       </c>
       <c r="G5" s="15" t="n">
         <v>455.7</v>
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>57.2%</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15458,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>155.33</v>
+        <v>156.58</v>
       </c>
     </row>
   </sheetData>
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>374235</v>
+        <v>374180</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>127432</v>
+        <v>127377</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>246803</v>
@@ -15568,10 +15568,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>173633</v>
+        <v>173579</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>66334</v>
+        <v>66279</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>107300</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>75,672 €</t>
+          <t>76,299 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>80.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>48,595 €</t>
+          <t>49,222 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -2273,10 +2273,10 @@
         <v>1660</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>3942.5</v>
+        <v>4357.5</v>
       </c>
       <c r="P21" s="13" t="n">
-        <v>563.21</v>
+        <v>622.5</v>
       </c>
     </row>
     <row r="22">
@@ -4553,10 +4553,10 @@
         <v>1416</v>
       </c>
       <c r="O53" s="17" t="n">
-        <v>1132.8</v>
+        <v>1345.2</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>647.3099999999999</v>
+        <v>768.6900000000001</v>
       </c>
     </row>
     <row r="54">
@@ -14119,10 +14119,10 @@
         <v>56423.7</v>
       </c>
       <c r="O193" s="19" t="n">
-        <v>75671.679</v>
+        <v>76299.079</v>
       </c>
       <c r="P193" s="19" t="n">
-        <v>200.32</v>
+        <v>201.98</v>
       </c>
     </row>
   </sheetData>
@@ -15543,10 +15543,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>374180</v>
+        <v>373553</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>127377</v>
+        <v>126750</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>246803</v>
@@ -15593,10 +15593,10 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>200601</v>
+        <v>199974</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>61098</v>
+        <v>60471</v>
       </c>
       <c r="D7" s="27" t="n">
         <v>139503</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -827,7 +827,7 @@
     <row r="16" ht="26" customHeight="1">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>639 h</t>
+          <t>645 h</t>
         </is>
       </c>
       <c r="B16" s="7" t="n"/>
@@ -841,7 +841,7 @@
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="9" t="inlineStr">
         <is>
-          <t>79.4%</t>
+          <t>80.1%</t>
         </is>
       </c>
       <c r="H16" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P193"/>
+  <dimension ref="A1:P194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -3385,7 +3385,7 @@
         <v>1</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L37" s="12" t="inlineStr">
         <is>
@@ -3404,7 +3404,7 @@
         <v>994.3200000000001</v>
       </c>
       <c r="P37" s="13" t="n">
-        <v>90.39</v>
+        <v>82.86</v>
       </c>
     </row>
     <row r="38">
@@ -6545,7 +6545,7 @@
         <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L81" s="12" t="inlineStr">
         <is>
@@ -6564,7 +6564,7 @@
         <v>882.5</v>
       </c>
       <c r="P81" s="13" t="n">
-        <v>3530</v>
+        <v>1765</v>
       </c>
     </row>
     <row r="82">
@@ -9767,7 +9767,7 @@
         <v>8</v>
       </c>
       <c r="K126" s="15" t="n">
-        <v>8</v>
+        <v>8.25</v>
       </c>
       <c r="L126" s="15" t="inlineStr">
         <is>
@@ -10410,26 +10410,28 @@
     <row r="136">
       <c r="A136" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-24209</t>
+          <t>PDMDEP-24216</t>
         </is>
       </c>
       <c r="B136" s="15" t="inlineStr">
         <is>
-          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
+          <t>MMM - LITTERALIS Script purge de données</t>
         </is>
       </c>
       <c r="C136" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D136" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE GENNEVILLIERS</t>
-        </is>
-      </c>
-      <c r="E136" s="15" t="n">
-        <v/>
+          <t>MONTPELLIER MEDITERRANEE METROPOLE</t>
+        </is>
+      </c>
+      <c r="E136" s="15" t="inlineStr">
+        <is>
+          <t>Script purge de données</t>
+        </is>
       </c>
       <c r="F136" s="15" t="inlineStr">
         <is>
@@ -10438,35 +10440,27 @@
       </c>
       <c r="G136" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H136" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I136" s="15" t="inlineStr">
         <is>
-          <t>09/09/2025</t>
+          <t>10/09/2025</t>
         </is>
       </c>
       <c r="J136" s="15" t="n">
         <v>10</v>
       </c>
       <c r="K136" s="15" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="L136" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27996</t>
-        </is>
-      </c>
-      <c r="M136" s="15" t="inlineStr">
-        <is>
-          <t>501219</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L136" s="15" t="inlineStr"/>
+      <c r="M136" s="15" t="inlineStr"/>
       <c r="N136" s="16" t="n">
         <v>0</v>
       </c>
@@ -10529,12 +10523,12 @@
       </c>
       <c r="L137" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27995</t>
+          <t>PDMDEP-27996</t>
         </is>
       </c>
       <c r="M137" s="12" t="inlineStr">
         <is>
-          <t>501218</t>
+          <t>501219</t>
         </is>
       </c>
       <c r="N137" s="13" t="n">
@@ -10550,22 +10544,22 @@
     <row r="138">
       <c r="A138" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24209</t>
         </is>
       </c>
       <c r="B138" s="15" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>[GENNEVILLIERS] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C138" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D138" s="15" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>VILLE DE GENNEVILLIERS</t>
         </is>
       </c>
       <c r="E138" s="15" t="n">
@@ -10588,54 +10582,54 @@
       </c>
       <c r="I138" s="15" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>09/09/2025</t>
         </is>
       </c>
       <c r="J138" s="15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K138" s="15" t="n">
-        <v>6</v>
+        <v>3.62</v>
       </c>
       <c r="L138" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27995</t>
         </is>
       </c>
       <c r="M138" s="15" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>501218</t>
         </is>
       </c>
       <c r="N138" s="16" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O138" s="17" t="n">
-        <v>832.374</v>
+        <v>0</v>
+      </c>
+      <c r="O138" s="16" t="n">
+        <v>0</v>
       </c>
       <c r="P138" s="16" t="n">
-        <v>138.73</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10643,7 +10637,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10653,49 +10647,49 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O139" s="13" t="n">
-        <v>964.1</v>
+        <v>2323</v>
+      </c>
+      <c r="O139" s="17" t="n">
+        <v>832.374</v>
       </c>
       <c r="P139" s="13" t="n">
-        <v>0</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
@@ -10739,19 +10733,19 @@
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O140" s="16" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="P140" s="16" t="n">
         <v>0</v>
@@ -10760,22 +10754,22 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D141" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E141" s="12" t="n">
@@ -10783,7 +10777,7 @@
       </c>
       <c r="F141" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -10793,35 +10787,35 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I141" s="12" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J141" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K141" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="13" t="n">
-        <v>0</v>
+        <v>140.4</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10830,22 +10824,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10863,59 +10857,59 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="16" t="n">
-        <v>126.2</v>
+        <v>0</v>
       </c>
       <c r="P142" s="16" t="n">
-        <v>63.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10933,38 +10927,38 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>0.19</v>
+        <v>2</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="13" t="n">
-        <v>0</v>
+        <v>126.2</v>
       </c>
       <c r="P143" s="13" t="n">
-        <v>0</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="144">
@@ -11019,12 +11013,12 @@
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
@@ -11055,7 +11049,7 @@
       </c>
       <c r="D145" s="12" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E145" s="12" t="n">
@@ -11089,12 +11083,12 @@
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
@@ -11125,7 +11119,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11159,12 +11153,12 @@
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11180,12 +11174,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B147" s="12" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
@@ -11195,7 +11189,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11213,28 +11207,28 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I147" s="12" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J147" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K147" s="12" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11250,22 +11244,22 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11288,23 +11282,23 @@
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K148" s="15" t="n">
         <v>0.5</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11320,22 +11314,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11343,7 +11337,7 @@
       </c>
       <c r="F149" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -11358,30 +11352,30 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K149" s="12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O149" s="13" t="n">
-        <v>482.72</v>
+        <v>0</v>
       </c>
       <c r="P149" s="13" t="n">
         <v>0</v>
@@ -11390,18 +11384,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C150" s="15" t="inlineStr"/>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+        </is>
+      </c>
+      <c r="C150" s="15" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11409,7 +11407,7 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
@@ -11435,19 +11433,19 @@
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>575</v>
+        <v>482.72</v>
       </c>
       <c r="P150" s="16" t="n">
         <v>0</v>
@@ -11456,22 +11454,18 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr"/>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11489,35 +11483,35 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I151" s="12" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J151" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K151" s="12" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="P151" s="13" t="n">
         <v>0</v>
@@ -11526,22 +11520,22 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C152" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11559,34 +11553,34 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>0.5</v>
+        <v>6.75</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
-        <v>250</v>
-      </c>
-      <c r="O152" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P152" s="16" t="n">
@@ -11596,22 +11590,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11634,54 +11628,54 @@
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>230</v>
-      </c>
-      <c r="O153" s="13" t="n">
-        <v>230</v>
+        <v>250</v>
+      </c>
+      <c r="O153" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
-        <v>102.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20217</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>CAP ATLANTIQUE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11689,7 +11683,7 @@
       </c>
       <c r="F154" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G154" s="15" t="inlineStr">
@@ -11704,54 +11698,54 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28028</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>464365</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="O154" s="16" t="n">
-        <v>660</v>
+        <v>230</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>0</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20217</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>CAP ATLANTIQUE</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11759,33 +11753,45 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H155" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H155" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L155" s="12" t="inlineStr"/>
-      <c r="M155" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L155" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28028</t>
+        </is>
+      </c>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>464365</t>
+        </is>
+      </c>
       <c r="N155" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O155" s="13" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="P155" s="13" t="n">
         <v>0</v>
@@ -11794,22 +11800,22 @@
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11822,35 +11828,23 @@
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H156" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H156" s="15" t="inlineStr"/>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>2</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M156" s="15" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr"/>
+      <c r="M156" s="15" t="inlineStr"/>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
@@ -11864,12 +11858,12 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
@@ -11879,7 +11873,7 @@
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11897,28 +11891,28 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L157" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M157" s="12" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N157" s="13" t="n">
@@ -11934,12 +11928,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11949,7 +11943,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11967,28 +11961,28 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
@@ -12004,12 +11998,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -12019,7 +12013,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -12042,23 +12036,23 @@
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N159" s="13" t="n">
@@ -12074,12 +12068,12 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
@@ -12089,13 +12083,11 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E160" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE D'ARCUEIL</t>
+        </is>
+      </c>
+      <c r="E160" s="15" t="n">
+        <v/>
       </c>
       <c r="F160" s="15" t="inlineStr">
         <is>
@@ -12104,27 +12096,35 @@
       </c>
       <c r="G160" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H160" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
         <v>17</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L160" s="15" t="inlineStr"/>
-      <c r="M160" s="15" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L160" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M160" s="15" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N160" s="16" t="n">
         <v>0</v>
       </c>
@@ -12138,26 +12138,28 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
@@ -12176,14 +12178,14 @@
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L161" s="12" t="inlineStr"/>
       <c r="M161" s="12" t="inlineStr"/>
@@ -12200,22 +12202,22 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E162" s="15" t="n">
@@ -12233,7 +12235,7 @@
       </c>
       <c r="H162" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I162" s="15" t="inlineStr">
@@ -12245,7 +12247,7 @@
         <v>19</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>5.25</v>
+        <v>0.75</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12262,22 +12264,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12285,7 +12287,7 @@
       </c>
       <c r="F163" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -12307,7 +12309,7 @@
         <v>19</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12324,12 +12326,12 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
@@ -12339,7 +12341,7 @@
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12352,39 +12354,31 @@
       </c>
       <c r="G164" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H164" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I164" s="15" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J164" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L164" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M164" s="15" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L164" s="15" t="inlineStr"/>
+      <c r="M164" s="15" t="inlineStr"/>
       <c r="N164" s="16" t="n">
-        <v>240</v>
-      </c>
-      <c r="O164" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O164" s="16" t="n">
         <v>0</v>
       </c>
       <c r="P164" s="16" t="n">
@@ -12394,22 +12388,22 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12417,7 +12411,7 @@
       </c>
       <c r="F165" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -12427,34 +12421,34 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L165" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M165" s="12" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N165" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O165" s="13" t="n">
+        <v>240</v>
+      </c>
+      <c r="O165" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P165" s="13" t="n">
@@ -12479,7 +12473,7 @@
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12513,7 +12507,7 @@
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
@@ -12534,22 +12528,22 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-17117</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B167" s="12" t="inlineStr">
         <is>
-          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C167" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>NÎMES</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12572,30 +12566,30 @@
       </c>
       <c r="I167" s="12" t="inlineStr">
         <is>
-          <t>14/10/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J167" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K167" s="12" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28005</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
         <is>
-          <t>448204</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N167" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O167" s="13" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="P167" s="13" t="n">
         <v>0</v>
@@ -12604,22 +12598,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17117</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>NÎMES</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12627,37 +12621,45 @@
       </c>
       <c r="F168" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G168" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H168" s="15" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L168" s="15" t="inlineStr"/>
-      <c r="M168" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L168" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28005</t>
+        </is>
+      </c>
+      <c r="M168" s="15" t="inlineStr">
+        <is>
+          <t>448204</t>
+        </is>
+      </c>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O168" s="16" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="P168" s="16" t="n">
         <v>0</v>
@@ -12666,22 +12668,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12689,7 +12691,7 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -12699,19 +12701,19 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>0.25</v>
+        <v>4.75</v>
       </c>
       <c r="L169" s="12" t="inlineStr"/>
       <c r="M169" s="12" t="inlineStr"/>
@@ -12728,22 +12730,22 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12766,25 +12768,17 @@
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>6</v>
-      </c>
-      <c r="L170" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M170" s="15" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L170" s="15" t="inlineStr"/>
+      <c r="M170" s="15" t="inlineStr"/>
       <c r="N170" s="16" t="n">
         <v>0</v>
       </c>
@@ -12798,12 +12792,12 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
@@ -12813,7 +12807,7 @@
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12836,17 +12830,25 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr"/>
-      <c r="M171" s="12" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12860,22 +12862,22 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12898,14 +12900,14 @@
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L172" s="15" t="inlineStr"/>
       <c r="M172" s="15" t="inlineStr"/>
@@ -12922,22 +12924,22 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -12960,14 +12962,14 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -12984,22 +12986,22 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E174" s="15" t="n">
@@ -13017,19 +13019,19 @@
       </c>
       <c r="H174" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -13046,22 +13048,22 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E175" s="12" t="n">
@@ -13079,19 +13081,19 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13108,12 +13110,12 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
@@ -13123,7 +13125,7 @@
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E176" s="15" t="n">
@@ -13136,7 +13138,7 @@
       </c>
       <c r="G176" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H176" s="15" t="inlineStr">
@@ -13146,25 +13148,17 @@
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L176" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M176" s="15" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L176" s="15" t="inlineStr"/>
+      <c r="M176" s="15" t="inlineStr"/>
       <c r="N176" s="16" t="n">
         <v>0</v>
       </c>
@@ -13178,22 +13172,22 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E177" s="12" t="n">
@@ -13206,23 +13200,35 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H177" s="12" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H177" s="12" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr"/>
-      <c r="M177" s="12" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N177" s="13" t="n">
         <v>0</v>
       </c>
@@ -13236,12 +13242,12 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
@@ -13251,7 +13257,7 @@
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E178" s="15" t="n">
@@ -13267,32 +13273,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H178" s="15" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H178" s="15" t="inlineStr"/>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M178" s="15" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr"/>
+      <c r="M178" s="15" t="inlineStr"/>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13306,12 +13300,12 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
@@ -13321,7 +13315,7 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E179" s="12" t="n">
@@ -13344,17 +13338,25 @@
       </c>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr"/>
-      <c r="M179" s="12" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13368,28 +13370,26 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E180" s="15" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E180" s="15" t="n">
+        <v/>
       </c>
       <c r="F180" s="15" t="inlineStr">
         <is>
@@ -13415,7 +13415,7 @@
         <v>34</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L180" s="15" t="inlineStr"/>
       <c r="M180" s="15" t="inlineStr"/>
@@ -13432,12 +13432,12 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
@@ -13447,12 +13447,12 @@
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E181" s="12" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -13467,7 +13467,7 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I181" s="12" t="inlineStr">
@@ -13479,7 +13479,7 @@
         <v>34</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13496,23 +13496,27 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C182" s="15" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C182" s="15" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
@@ -13527,19 +13531,19 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J182" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>1.75</v>
+        <v>9.5</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13556,21 +13560,25 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C183" s="12" t="inlineStr"/>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="E183" s="12" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E183" s="12" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F183" s="12" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13578,20 +13586,24 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H183" s="12" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H183" s="12" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L183" s="12" t="inlineStr"/>
       <c r="M183" s="12" t="inlineStr"/>
@@ -13608,18 +13620,18 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E184" s="15" t="inlineStr"/>
@@ -13636,7 +13648,7 @@
       <c r="H184" s="15" t="inlineStr"/>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
@@ -13660,18 +13672,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1310</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13688,14 +13700,14 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K185" s="12" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L185" s="12" t="inlineStr"/>
       <c r="M185" s="12" t="inlineStr"/>
@@ -13712,18 +13724,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1310</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13734,36 +13746,28 @@
       </c>
       <c r="G186" s="15" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L186" s="15" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M186" s="15" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L186" s="15" t="inlineStr"/>
+      <c r="M186" s="15" t="inlineStr"/>
       <c r="N186" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O186" s="16" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P186" s="16" t="n">
         <v>0</v>
@@ -13772,18 +13776,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13800,50 +13804,50 @@
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L187" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M187" s="12" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N187" s="13" t="n">
-        <v>510.6</v>
+        <v>0</v>
       </c>
       <c r="O187" s="13" t="n">
-        <v>680.8</v>
+        <v>150</v>
       </c>
       <c r="P187" s="13" t="n">
-        <v>247.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13860,50 +13864,50 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L188" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33167</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M188" s="15" t="inlineStr">
         <is>
-          <t>00165437</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N188" s="16" t="n">
-        <v>0</v>
+        <v>510.6</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>100</v>
+        <v>680.8</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>0</v>
+        <v>247.56</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13914,28 +13918,36 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L189" s="12" t="inlineStr"/>
-      <c r="M189" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L189" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-33167</t>
+        </is>
+      </c>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>00165437</t>
+        </is>
+      </c>
       <c r="N189" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O189" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P189" s="13" t="n">
         <v>0</v>
@@ -13944,18 +13956,18 @@
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13972,14 +13984,14 @@
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L190" s="15" t="inlineStr"/>
       <c r="M190" s="15" t="inlineStr"/>
@@ -13996,18 +14008,18 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -14024,14 +14036,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -14048,18 +14060,18 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1021</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="E192" s="15" t="inlineStr"/>
@@ -14076,11 +14088,11 @@
       <c r="H192" s="15" t="inlineStr"/>
       <c r="I192" s="15" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J192" s="15" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K192" s="15" t="n">
         <v>0.5</v>
@@ -14098,31 +14110,83 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="18" t="inlineStr">
+      <c r="A193" s="11" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B193" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr"/>
+      <c r="D193" s="12" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E193" s="12" t="inlineStr"/>
+      <c r="F193" s="12" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G193" s="12" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H193" s="12" t="inlineStr"/>
+      <c r="I193" s="12" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J193" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K193" s="12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L193" s="12" t="inlineStr"/>
+      <c r="M193" s="12" t="inlineStr"/>
+      <c r="N193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P193" s="13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B193" s="18" t="inlineStr"/>
-      <c r="C193" s="18" t="inlineStr"/>
-      <c r="D193" s="18" t="inlineStr"/>
-      <c r="E193" s="18" t="inlineStr"/>
-      <c r="F193" s="18" t="inlineStr"/>
-      <c r="G193" s="18" t="inlineStr"/>
-      <c r="H193" s="18" t="inlineStr"/>
-      <c r="I193" s="18" t="inlineStr"/>
-      <c r="J193" s="18" t="inlineStr"/>
-      <c r="K193" s="18" t="inlineStr"/>
-      <c r="L193" s="18" t="inlineStr"/>
-      <c r="M193" s="18" t="inlineStr"/>
-      <c r="N193" s="19" t="n">
+      <c r="B194" s="18" t="inlineStr"/>
+      <c r="C194" s="18" t="inlineStr"/>
+      <c r="D194" s="18" t="inlineStr"/>
+      <c r="E194" s="18" t="inlineStr"/>
+      <c r="F194" s="18" t="inlineStr"/>
+      <c r="G194" s="18" t="inlineStr"/>
+      <c r="H194" s="18" t="inlineStr"/>
+      <c r="I194" s="18" t="inlineStr"/>
+      <c r="J194" s="18" t="inlineStr"/>
+      <c r="K194" s="18" t="inlineStr"/>
+      <c r="L194" s="18" t="inlineStr"/>
+      <c r="M194" s="18" t="inlineStr"/>
+      <c r="N194" s="19" t="n">
         <v>56423.7</v>
       </c>
-      <c r="O193" s="19" t="n">
+      <c r="O194" s="19" t="n">
         <v>76299.079</v>
       </c>
-      <c r="P193" s="19" t="n">
-        <v>201.98</v>
+      <c r="P194" s="19" t="n">
+        <v>200.65</v>
       </c>
     </row>
   </sheetData>
@@ -14316,6 +14380,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId186"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15397,16 +15462,16 @@
         </is>
       </c>
       <c r="B5" s="15" t="n">
-        <v>209.25</v>
+        <v>211.25</v>
       </c>
       <c r="C5" s="15" t="n">
-        <v>45.5</v>
+        <v>46</v>
       </c>
       <c r="D5" s="15" t="n">
         <v>6</v>
       </c>
       <c r="E5" s="15" t="n">
-        <v>260.75</v>
+        <v>263.25</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>81</v>
@@ -15416,7 +15481,7 @@
       </c>
       <c r="H5" s="22" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -15458,7 +15523,7 @@
         </is>
       </c>
       <c r="B8" s="24" t="n">
-        <v>156.58</v>
+        <v>159.83</v>
       </c>
     </row>
   </sheetData>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>76,299 €</t>
+          <t>77,197 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>80.3%</t>
+          <t>81.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -779,7 +779,7 @@
       <c r="C11" s="7" t="n"/>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>49,222 €</t>
+          <t>50,121 €</t>
         </is>
       </c>
       <c r="E11" s="7" t="n"/>
@@ -945,7 +945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P194"/>
+  <dimension ref="A1:P195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="43" customWidth="1" min="1" max="1"/>
@@ -4552,11 +4552,11 @@
       <c r="N53" s="13" t="n">
         <v>1416</v>
       </c>
-      <c r="O53" s="17" t="n">
-        <v>1345.2</v>
+      <c r="O53" s="13" t="n">
+        <v>1557.6</v>
       </c>
       <c r="P53" s="13" t="n">
-        <v>768.6900000000001</v>
+        <v>890.0599999999999</v>
       </c>
     </row>
     <row r="54">
@@ -10614,22 +10614,22 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23918</t>
+          <t>PDMDEP-24061</t>
         </is>
       </c>
       <c r="B139" s="12" t="inlineStr">
         <is>
-          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
+          <t>COMMUNE D' ANTIBES - GEODP2 migration</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D139" s="12" t="inlineStr">
         <is>
-          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
+          <t>COMMUNE D'ANTIBES</t>
         </is>
       </c>
       <c r="E139" s="12" t="n">
@@ -10637,7 +10637,7 @@
       </c>
       <c r="F139" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -10647,59 +10647,59 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I139" s="12" t="inlineStr">
         <is>
-          <t>26/08/2025</t>
+          <t>28/08/2025</t>
         </is>
       </c>
       <c r="J139" s="12" t="n">
         <v>11</v>
       </c>
       <c r="K139" s="12" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="L139" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28055</t>
+          <t>PDMDEP-27034</t>
         </is>
       </c>
       <c r="M139" s="12" t="inlineStr">
         <is>
-          <t>499132</t>
+          <t>488524</t>
         </is>
       </c>
       <c r="N139" s="13" t="n">
-        <v>2323</v>
-      </c>
-      <c r="O139" s="17" t="n">
-        <v>832.374</v>
+        <v>0</v>
+      </c>
+      <c r="O139" s="13" t="n">
+        <v>685.9400000000001</v>
       </c>
       <c r="P139" s="13" t="n">
-        <v>128.06</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23486</t>
+          <t>PDMDEP-23918</t>
         </is>
       </c>
       <c r="B140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
+          <t>[CD94 - VAL DE MARNE] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C140" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D140" s="15" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>DEPARTEMENT DU VAL DE MARNE (CD 94)</t>
         </is>
       </c>
       <c r="E140" s="15" t="n">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="F140" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G140" s="15" t="inlineStr">
@@ -10717,49 +10717,49 @@
       </c>
       <c r="H140" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I140" s="15" t="inlineStr">
         <is>
-          <t>25/07/2025</t>
+          <t>26/08/2025</t>
         </is>
       </c>
       <c r="J140" s="15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K140" s="15" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="L140" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27493</t>
+          <t>PDMDEP-28055</t>
         </is>
       </c>
       <c r="M140" s="15" t="inlineStr">
         <is>
-          <t>495699</t>
+          <t>499132</t>
         </is>
       </c>
       <c r="N140" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O140" s="16" t="n">
-        <v>964.1</v>
+        <v>2323</v>
+      </c>
+      <c r="O140" s="17" t="n">
+        <v>832.374</v>
       </c>
       <c r="P140" s="16" t="n">
-        <v>0</v>
+        <v>128.06</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-23484</t>
+          <t>PDMDEP-23486</t>
         </is>
       </c>
       <c r="B141" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
+          <t>METROPOLE TOULON- AJOUT BALISE FILIEN</t>
         </is>
       </c>
       <c r="C141" s="12" t="inlineStr">
@@ -10803,19 +10803,19 @@
       </c>
       <c r="L141" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27494</t>
+          <t>PDMDEP-27493</t>
         </is>
       </c>
       <c r="M141" s="12" t="inlineStr">
         <is>
-          <t>495695</t>
+          <t>495699</t>
         </is>
       </c>
       <c r="N141" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O141" s="13" t="n">
-        <v>140.4</v>
+        <v>964.1</v>
       </c>
       <c r="P141" s="13" t="n">
         <v>0</v>
@@ -10824,22 +10824,22 @@
     <row r="142">
       <c r="A142" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-23323</t>
+          <t>PDMDEP-23484</t>
         </is>
       </c>
       <c r="B142" s="15" t="inlineStr">
         <is>
-          <t>[BAGNOLET] - LITTERALIS projet</t>
+          <t>METROPOLE TOULON- AJOUT LIEU DE NAISSANCE DANS FILIEN</t>
         </is>
       </c>
       <c r="C142" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D142" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE BAGNOLET</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E142" s="15" t="n">
@@ -10847,7 +10847,7 @@
       </c>
       <c r="F142" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G142" s="15" t="inlineStr">
@@ -10857,35 +10857,35 @@
       </c>
       <c r="H142" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I142" s="15" t="inlineStr">
         <is>
-          <t>21/07/2025</t>
+          <t>25/07/2025</t>
         </is>
       </c>
       <c r="J142" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K142" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27570</t>
+          <t>PDMDEP-27494</t>
         </is>
       </c>
       <c r="M142" s="15" t="inlineStr">
         <is>
-          <t>493613</t>
+          <t>495695</t>
         </is>
       </c>
       <c r="N142" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O142" s="16" t="n">
-        <v>0</v>
+        <v>140.4</v>
       </c>
       <c r="P142" s="16" t="n">
         <v>0</v>
@@ -10894,22 +10894,22 @@
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-22996</t>
+          <t>PDMDEP-23323</t>
         </is>
       </c>
       <c r="B143" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
+          <t>[BAGNOLET] - LITTERALIS projet</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D143" s="12" t="inlineStr">
         <is>
-          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
+          <t>VILLE DE BAGNOLET</t>
         </is>
       </c>
       <c r="E143" s="12" t="n">
@@ -10927,59 +10927,59 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I143" s="12" t="inlineStr">
         <is>
-          <t>07/07/2025</t>
+          <t>21/07/2025</t>
         </is>
       </c>
       <c r="J143" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K143" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L143" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28051</t>
+          <t>PDMDEP-27570</t>
         </is>
       </c>
       <c r="M143" s="12" t="inlineStr">
         <is>
-          <t>487190</t>
+          <t>493613</t>
         </is>
       </c>
       <c r="N143" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O143" s="13" t="n">
-        <v>126.2</v>
+        <v>0</v>
       </c>
       <c r="P143" s="13" t="n">
-        <v>63.1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22757</t>
+          <t>PDMDEP-22996</t>
         </is>
       </c>
       <c r="B144" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE - LITTERALIS</t>
         </is>
       </c>
       <c r="C144" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D144" s="15" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>METROPOLE TOULON-PROVENCE-MEDITERRANEE</t>
         </is>
       </c>
       <c r="E144" s="15" t="n">
@@ -10997,38 +10997,38 @@
       </c>
       <c r="H144" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I144" s="15" t="inlineStr">
         <is>
-          <t>01/07/2025</t>
+          <t>07/07/2025</t>
         </is>
       </c>
       <c r="J144" s="15" t="n">
         <v>12</v>
       </c>
       <c r="K144" s="15" t="n">
-        <v>0.19</v>
+        <v>2</v>
       </c>
       <c r="L144" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30081</t>
+          <t>PDMDEP-28051</t>
         </is>
       </c>
       <c r="M144" s="15" t="inlineStr">
         <is>
-          <t>00152628</t>
+          <t>487190</t>
         </is>
       </c>
       <c r="N144" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O144" s="16" t="n">
-        <v>0</v>
+        <v>126.2</v>
       </c>
       <c r="P144" s="16" t="n">
-        <v>0</v>
+        <v>63.1</v>
       </c>
     </row>
     <row r="145">
@@ -11083,12 +11083,12 @@
       </c>
       <c r="L145" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-30080</t>
+          <t>PDMDEP-30081</t>
         </is>
       </c>
       <c r="M145" s="12" t="inlineStr">
         <is>
-          <t>00152635</t>
+          <t>00152628</t>
         </is>
       </c>
       <c r="N145" s="13" t="n">
@@ -11119,7 +11119,7 @@
       </c>
       <c r="D146" s="15" t="inlineStr">
         <is>
-          <t>Brest Métropole</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E146" s="15" t="n">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="L146" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-30079</t>
+          <t>PDMDEP-30080</t>
         </is>
       </c>
       <c r="M146" s="15" t="inlineStr">
         <is>
-          <t>00152632</t>
+          <t>00152635</t>
         </is>
       </c>
       <c r="N146" s="16" t="n">
@@ -11189,7 +11189,7 @@
       </c>
       <c r="D147" s="12" t="inlineStr">
         <is>
-          <t>BREST METROPOLE</t>
+          <t>Brest Métropole</t>
         </is>
       </c>
       <c r="E147" s="12" t="n">
@@ -11223,12 +11223,12 @@
       </c>
       <c r="L147" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27365</t>
+          <t>PDMDEP-30079</t>
         </is>
       </c>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>491593</t>
+          <t>00152632</t>
         </is>
       </c>
       <c r="N147" s="13" t="n">
@@ -11244,12 +11244,12 @@
     <row r="148">
       <c r="A148" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-22496</t>
+          <t>PDMDEP-22757</t>
         </is>
       </c>
       <c r="B148" s="15" t="inlineStr">
         <is>
-          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
+          <t>BREST METROPOLE - DEPLOIEMENT DE LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C148" s="15" t="inlineStr">
@@ -11259,7 +11259,7 @@
       </c>
       <c r="D148" s="15" t="inlineStr">
         <is>
-          <t>VILLE DE VILLEJUIF</t>
+          <t>BREST METROPOLE</t>
         </is>
       </c>
       <c r="E148" s="15" t="n">
@@ -11277,28 +11277,28 @@
       </c>
       <c r="H148" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I148" s="15" t="inlineStr">
         <is>
-          <t>23/06/2025</t>
+          <t>01/07/2025</t>
         </is>
       </c>
       <c r="J148" s="15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K148" s="15" t="n">
-        <v>0.5</v>
+        <v>0.19</v>
       </c>
       <c r="L148" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27371</t>
+          <t>PDMDEP-27365</t>
         </is>
       </c>
       <c r="M148" s="15" t="inlineStr">
         <is>
-          <t>481817</t>
+          <t>491593</t>
         </is>
       </c>
       <c r="N148" s="16" t="n">
@@ -11314,22 +11314,22 @@
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21661</t>
+          <t>PDMDEP-22496</t>
         </is>
       </c>
       <c r="B149" s="12" t="inlineStr">
         <is>
-          <t>[Grand Dax] - Pastell</t>
+          <t>[VILLEJUIF] - LITTERALIS Pastell</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D149" s="12" t="inlineStr">
         <is>
-          <t>GRAND DAX</t>
+          <t>VILLE DE VILLEJUIF</t>
         </is>
       </c>
       <c r="E149" s="12" t="n">
@@ -11352,23 +11352,23 @@
       </c>
       <c r="I149" s="12" t="inlineStr">
         <is>
-          <t>07/05/2025</t>
+          <t>23/06/2025</t>
         </is>
       </c>
       <c r="J149" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K149" s="12" t="n">
         <v>0.5</v>
       </c>
       <c r="L149" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27373</t>
+          <t>PDMDEP-27371</t>
         </is>
       </c>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>466234</t>
+          <t>481817</t>
         </is>
       </c>
       <c r="N149" s="13" t="n">
@@ -11384,22 +11384,22 @@
     <row r="150">
       <c r="A150" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21546</t>
+          <t>PDMDEP-21661</t>
         </is>
       </c>
       <c r="B150" s="15" t="inlineStr">
         <is>
-          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+          <t>[Grand Dax] - Pastell</t>
         </is>
       </c>
       <c r="C150" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D150" s="15" t="inlineStr">
         <is>
-          <t>VILLEURBANNE</t>
+          <t>GRAND DAX</t>
         </is>
       </c>
       <c r="E150" s="15" t="n">
@@ -11407,7 +11407,7 @@
       </c>
       <c r="F150" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G150" s="15" t="inlineStr">
@@ -11422,30 +11422,30 @@
       </c>
       <c r="I150" s="15" t="inlineStr">
         <is>
-          <t>05/05/2025</t>
+          <t>07/05/2025</t>
         </is>
       </c>
       <c r="J150" s="15" t="n">
         <v>14</v>
       </c>
       <c r="K150" s="15" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="L150" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28038</t>
+          <t>PDMDEP-27373</t>
         </is>
       </c>
       <c r="M150" s="15" t="inlineStr">
         <is>
-          <t>478867</t>
+          <t>466234</t>
         </is>
       </c>
       <c r="N150" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O150" s="16" t="n">
-        <v>482.72</v>
+        <v>0</v>
       </c>
       <c r="P150" s="16" t="n">
         <v>0</v>
@@ -11454,18 +11454,22 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21544</t>
+          <t>PDMDEP-21546</t>
         </is>
       </c>
       <c r="B151" s="12" t="inlineStr">
         <is>
-          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr"/>
+          <t>[Villeurbanne] Evolution produit - impression des tickets d'infraction et de présence</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>Alizée MARGOT</t>
+        </is>
+      </c>
       <c r="D151" s="12" t="inlineStr">
         <is>
-          <t>LA CIOTAT</t>
+          <t>VILLEURBANNE</t>
         </is>
       </c>
       <c r="E151" s="12" t="n">
@@ -11473,7 +11477,7 @@
       </c>
       <c r="F151" s="12" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -11499,19 +11503,19 @@
       </c>
       <c r="L151" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28037</t>
+          <t>PDMDEP-28038</t>
         </is>
       </c>
       <c r="M151" s="12" t="inlineStr">
         <is>
-          <t>474055</t>
+          <t>478867</t>
         </is>
       </c>
       <c r="N151" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O151" s="13" t="n">
-        <v>575</v>
+        <v>482.72</v>
       </c>
       <c r="P151" s="13" t="n">
         <v>0</v>
@@ -11520,22 +11524,18 @@
     <row r="152">
       <c r="A152" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-21222</t>
+          <t>PDMDEP-21544</t>
         </is>
       </c>
       <c r="B152" s="15" t="inlineStr">
         <is>
-          <t>[Issy les Moulineaux] Litteralis Expert</t>
-        </is>
-      </c>
-      <c r="C152" s="15" t="inlineStr">
-        <is>
-          <t>Fabien REUTENAUER</t>
-        </is>
-      </c>
+          <t>[La Ciotat] Accompagnement modélisation Littéralis Expert</t>
+        </is>
+      </c>
+      <c r="C152" s="15" t="inlineStr"/>
       <c r="D152" s="15" t="inlineStr">
         <is>
-          <t>ISSY LES MOULINEAUX</t>
+          <t>LA CIOTAT</t>
         </is>
       </c>
       <c r="E152" s="15" t="n">
@@ -11553,35 +11553,35 @@
       </c>
       <c r="H152" s="15" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I152" s="15" t="inlineStr">
         <is>
-          <t>23/04/2025</t>
+          <t>05/05/2025</t>
         </is>
       </c>
       <c r="J152" s="15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="K152" s="15" t="n">
-        <v>6.75</v>
+        <v>0</v>
       </c>
       <c r="L152" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28036</t>
+          <t>PDMDEP-28037</t>
         </is>
       </c>
       <c r="M152" s="15" t="inlineStr">
         <is>
-          <t>483799</t>
+          <t>474055</t>
         </is>
       </c>
       <c r="N152" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O152" s="16" t="n">
-        <v>0</v>
+        <v>575</v>
       </c>
       <c r="P152" s="16" t="n">
         <v>0</v>
@@ -11590,22 +11590,22 @@
     <row r="153">
       <c r="A153" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-21165</t>
+          <t>PDMDEP-21222</t>
         </is>
       </c>
       <c r="B153" s="12" t="inlineStr">
         <is>
-          <t>[Montreuil] Mise à jour carto (SaaS)</t>
+          <t>[Issy les Moulineaux] Litteralis Expert</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D153" s="12" t="inlineStr">
         <is>
-          <t>MONTREUIL</t>
+          <t>ISSY LES MOULINEAUX</t>
         </is>
       </c>
       <c r="E153" s="12" t="n">
@@ -11623,34 +11623,34 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I153" s="12" t="inlineStr">
         <is>
-          <t>18/04/2025</t>
+          <t>23/04/2025</t>
         </is>
       </c>
       <c r="J153" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K153" s="12" t="n">
-        <v>0.5</v>
+        <v>6.75</v>
       </c>
       <c r="L153" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28035</t>
+          <t>PDMDEP-28036</t>
         </is>
       </c>
       <c r="M153" s="12" t="inlineStr">
         <is>
-          <t>468660</t>
+          <t>483799</t>
         </is>
       </c>
       <c r="N153" s="13" t="n">
-        <v>250</v>
-      </c>
-      <c r="O153" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O153" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P153" s="13" t="n">
@@ -11660,22 +11660,22 @@
     <row r="154">
       <c r="A154" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20907</t>
+          <t>PDMDEP-21165</t>
         </is>
       </c>
       <c r="B154" s="15" t="inlineStr">
         <is>
-          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
+          <t>[Montreuil] Mise à jour carto (SaaS)</t>
         </is>
       </c>
       <c r="C154" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D154" s="15" t="inlineStr">
         <is>
-          <t>SAINT PIERRE (LA REUNION)</t>
+          <t>MONTREUIL</t>
         </is>
       </c>
       <c r="E154" s="15" t="n">
@@ -11698,54 +11698,54 @@
       </c>
       <c r="I154" s="15" t="inlineStr">
         <is>
-          <t>14/04/2025</t>
+          <t>18/04/2025</t>
         </is>
       </c>
       <c r="J154" s="15" t="n">
         <v>15</v>
       </c>
       <c r="K154" s="15" t="n">
-        <v>2.25</v>
+        <v>0.5</v>
       </c>
       <c r="L154" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28034</t>
+          <t>PDMDEP-28035</t>
         </is>
       </c>
       <c r="M154" s="15" t="inlineStr">
         <is>
-          <t>475575</t>
+          <t>468660</t>
         </is>
       </c>
       <c r="N154" s="16" t="n">
-        <v>230</v>
-      </c>
-      <c r="O154" s="16" t="n">
-        <v>230</v>
+        <v>250</v>
+      </c>
+      <c r="O154" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>102.22</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20217</t>
+          <t>PDMDEP-20907</t>
         </is>
       </c>
       <c r="B155" s="12" t="inlineStr">
         <is>
-          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
+          <t>[Saint-Pierre (Réunion)] Accompagnement modélisation AME Littéralis Expert</t>
         </is>
       </c>
       <c r="C155" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D155" s="12" t="inlineStr">
         <is>
-          <t>CAP ATLANTIQUE</t>
+          <t>SAINT PIERRE (LA REUNION)</t>
         </is>
       </c>
       <c r="E155" s="12" t="n">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="F155" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -11768,54 +11768,54 @@
       </c>
       <c r="I155" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>14/04/2025</t>
         </is>
       </c>
       <c r="J155" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K155" s="12" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="L155" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28028</t>
+          <t>PDMDEP-28034</t>
         </is>
       </c>
       <c r="M155" s="12" t="inlineStr">
         <is>
-          <t>464365</t>
+          <t>475575</t>
         </is>
       </c>
       <c r="N155" s="13" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="O155" s="13" t="n">
-        <v>660</v>
+        <v>230</v>
       </c>
       <c r="P155" s="13" t="n">
-        <v>0</v>
+        <v>102.22</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-20187</t>
+          <t>PDMDEP-20217</t>
         </is>
       </c>
       <c r="B156" s="15" t="inlineStr">
         <is>
-          <t>[ANTIBES] - Interface AIRS Delib</t>
+          <t>[CAP Atlantique] Export Astre &amp; SEPA</t>
         </is>
       </c>
       <c r="C156" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D156" s="15" t="inlineStr">
         <is>
-          <t>Antibes</t>
+          <t>CAP ATLANTIQUE</t>
         </is>
       </c>
       <c r="E156" s="15" t="n">
@@ -11823,33 +11823,45 @@
       </c>
       <c r="F156" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G156" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H156" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H156" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I156" s="15" t="inlineStr">
         <is>
-          <t>19/03/2025</t>
+          <t>20/03/2025</t>
         </is>
       </c>
       <c r="J156" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K156" s="15" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L156" s="15" t="inlineStr"/>
-      <c r="M156" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L156" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28028</t>
+        </is>
+      </c>
+      <c r="M156" s="15" t="inlineStr">
+        <is>
+          <t>464365</t>
+        </is>
+      </c>
       <c r="N156" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O156" s="16" t="n">
-        <v>0</v>
+        <v>660</v>
       </c>
       <c r="P156" s="16" t="n">
         <v>0</v>
@@ -11858,22 +11870,22 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-20032</t>
+          <t>PDMDEP-20187</t>
         </is>
       </c>
       <c r="B157" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[SENS] Littéralis Expert </t>
+          <t>[ANTIBES] - Interface AIRS Delib</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D157" s="12" t="inlineStr">
         <is>
-          <t>SENS</t>
+          <t>Antibes</t>
         </is>
       </c>
       <c r="E157" s="12" t="n">
@@ -11886,35 +11898,23 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
-        </is>
-      </c>
-      <c r="H157" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H157" s="12" t="inlineStr"/>
       <c r="I157" s="12" t="inlineStr">
         <is>
-          <t>14/03/2025</t>
+          <t>19/03/2025</t>
         </is>
       </c>
       <c r="J157" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K157" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L157" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28027</t>
-        </is>
-      </c>
-      <c r="M157" s="12" t="inlineStr">
-        <is>
-          <t>470688</t>
-        </is>
-      </c>
+        <v>2.75</v>
+      </c>
+      <c r="L157" s="12" t="inlineStr"/>
+      <c r="M157" s="12" t="inlineStr"/>
       <c r="N157" s="13" t="n">
         <v>0</v>
       </c>
@@ -11928,12 +11928,12 @@
     <row r="158">
       <c r="A158" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19909</t>
+          <t>PDMDEP-20032</t>
         </is>
       </c>
       <c r="B158" s="15" t="inlineStr">
         <is>
-          <t>[CD 29] Interface Pastell</t>
+          <t xml:space="preserve">[SENS] Littéralis Expert </t>
         </is>
       </c>
       <c r="C158" s="15" t="inlineStr">
@@ -11943,7 +11943,7 @@
       </c>
       <c r="D158" s="15" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
+          <t>SENS</t>
         </is>
       </c>
       <c r="E158" s="15" t="n">
@@ -11961,28 +11961,28 @@
       </c>
       <c r="H158" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I158" s="15" t="inlineStr">
         <is>
-          <t>11/03/2025</t>
+          <t>14/03/2025</t>
         </is>
       </c>
       <c r="J158" s="15" t="n">
         <v>16</v>
       </c>
       <c r="K158" s="15" t="n">
-        <v>0.25</v>
+        <v>2</v>
       </c>
       <c r="L158" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27568</t>
+          <t>PDMDEP-28027</t>
         </is>
       </c>
       <c r="M158" s="15" t="inlineStr">
         <is>
-          <t>471958</t>
+          <t>470688</t>
         </is>
       </c>
       <c r="N158" s="16" t="n">
@@ -11998,12 +11998,12 @@
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-19792</t>
+          <t>PDMDEP-19909</t>
         </is>
       </c>
       <c r="B159" s="12" t="inlineStr">
         <is>
-          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
+          <t>[CD 29] Interface Pastell</t>
         </is>
       </c>
       <c r="C159" s="12" t="inlineStr">
@@ -12013,7 +12013,7 @@
       </c>
       <c r="D159" s="12" t="inlineStr">
         <is>
-          <t>VIENNE CONDRIEU AGGLOMERATION</t>
+          <t>CONSEIL DEPARTEMENTAL DU FINISTERE (CD29)</t>
         </is>
       </c>
       <c r="E159" s="12" t="n">
@@ -12031,28 +12031,28 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I159" s="12" t="inlineStr">
         <is>
-          <t>06/03/2025</t>
+          <t>11/03/2025</t>
         </is>
       </c>
       <c r="J159" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K159" s="12" t="n">
-        <v>1.75</v>
+        <v>0.25</v>
       </c>
       <c r="L159" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-27377</t>
+          <t>PDMDEP-27568</t>
         </is>
       </c>
       <c r="M159" s="12" t="inlineStr">
         <is>
-          <t>478048</t>
+          <t>471958</t>
         </is>
       </c>
       <c r="N159" s="13" t="n">
@@ -12068,12 +12068,12 @@
     <row r="160">
       <c r="A160" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-19385</t>
+          <t>PDMDEP-19792</t>
         </is>
       </c>
       <c r="B160" s="15" t="inlineStr">
         <is>
-          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
+          <t xml:space="preserve">[Vienne Condrieu Agglomération] Litt PRIME + DA/DPA + Flux WFS + Abo ville de Vienne + Param </t>
         </is>
       </c>
       <c r="C160" s="15" t="inlineStr">
@@ -12083,7 +12083,7 @@
       </c>
       <c r="D160" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE D'ARCUEIL</t>
+          <t>VIENNE CONDRIEU AGGLOMERATION</t>
         </is>
       </c>
       <c r="E160" s="15" t="n">
@@ -12106,23 +12106,23 @@
       </c>
       <c r="I160" s="15" t="inlineStr">
         <is>
-          <t>24/02/2025</t>
+          <t>06/03/2025</t>
         </is>
       </c>
       <c r="J160" s="15" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="K160" s="15" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="L160" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-27535</t>
+          <t>PDMDEP-27377</t>
         </is>
       </c>
       <c r="M160" s="15" t="inlineStr">
         <is>
-          <t>465345</t>
+          <t>478048</t>
         </is>
       </c>
       <c r="N160" s="16" t="n">
@@ -12138,12 +12138,12 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18954</t>
+          <t>PDMDEP-19385</t>
         </is>
       </c>
       <c r="B161" s="12" t="inlineStr">
         <is>
-          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
+          <t>[Arcueil] Litt Exp + 2 options + modélisation + formations</t>
         </is>
       </c>
       <c r="C161" s="12" t="inlineStr">
@@ -12153,13 +12153,11 @@
       </c>
       <c r="D161" s="12" t="inlineStr">
         <is>
-          <t>Maisons-Alfort</t>
-        </is>
-      </c>
-      <c r="E161" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement Littéralis Expert</t>
-        </is>
+          <t>COMMUNE D'ARCUEIL</t>
+        </is>
+      </c>
+      <c r="E161" s="12" t="n">
+        <v/>
       </c>
       <c r="F161" s="12" t="inlineStr">
         <is>
@@ -12168,27 +12166,35 @@
       </c>
       <c r="G161" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I161" s="12" t="inlineStr">
         <is>
-          <t>05/02/2025</t>
+          <t>24/02/2025</t>
         </is>
       </c>
       <c r="J161" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K161" s="12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="L161" s="12" t="inlineStr"/>
-      <c r="M161" s="12" t="inlineStr"/>
+        <v>1.5</v>
+      </c>
+      <c r="L161" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-27535</t>
+        </is>
+      </c>
+      <c r="M161" s="12" t="inlineStr">
+        <is>
+          <t>465345</t>
+        </is>
+      </c>
       <c r="N161" s="13" t="n">
         <v>0</v>
       </c>
@@ -12202,26 +12208,28 @@
     <row r="162">
       <c r="A162" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18241</t>
+          <t>PDMDEP-18954</t>
         </is>
       </c>
       <c r="B162" s="15" t="inlineStr">
         <is>
-          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
+          <t>[Maisons-Alfort] - Déploiement Littéralis Expert</t>
         </is>
       </c>
       <c r="C162" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D162" s="15" t="inlineStr">
         <is>
-          <t>CD 74 - HAUTE SAVOIE</t>
-        </is>
-      </c>
-      <c r="E162" s="15" t="n">
-        <v/>
+          <t>Maisons-Alfort</t>
+        </is>
+      </c>
+      <c r="E162" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Littéralis Expert</t>
+        </is>
       </c>
       <c r="F162" s="15" t="inlineStr">
         <is>
@@ -12240,14 +12248,14 @@
       </c>
       <c r="I162" s="15" t="inlineStr">
         <is>
-          <t>20/12/2024</t>
+          <t>05/02/2025</t>
         </is>
       </c>
       <c r="J162" s="15" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K162" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L162" s="15" t="inlineStr"/>
       <c r="M162" s="15" t="inlineStr"/>
@@ -12264,22 +12272,22 @@
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18240</t>
+          <t>PDMDEP-18241</t>
         </is>
       </c>
       <c r="B163" s="12" t="inlineStr">
         <is>
-          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
+          <t>[CD74 - HAUTE SAVOIE] - Interface LiEx Maj Ref BG</t>
         </is>
       </c>
       <c r="C163" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D163" s="12" t="inlineStr">
         <is>
-          <t>Biarritz</t>
+          <t>CD 74 - HAUTE SAVOIE</t>
         </is>
       </c>
       <c r="E163" s="12" t="n">
@@ -12297,7 +12305,7 @@
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I163" s="12" t="inlineStr">
@@ -12309,7 +12317,7 @@
         <v>19</v>
       </c>
       <c r="K163" s="12" t="n">
-        <v>5.25</v>
+        <v>0.75</v>
       </c>
       <c r="L163" s="12" t="inlineStr"/>
       <c r="M163" s="12" t="inlineStr"/>
@@ -12326,22 +12334,22 @@
     <row r="164">
       <c r="A164" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18212</t>
+          <t>PDMDEP-18240</t>
         </is>
       </c>
       <c r="B164" s="15" t="inlineStr">
         <is>
-          <t>[Besancon] Acquisition</t>
+          <t>[BIARRITZ] - Projet Littéralis Expert (Cmde1 - Mise en service - abo)</t>
         </is>
       </c>
       <c r="C164" s="15" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D164" s="15" t="inlineStr">
         <is>
-          <t>Besançon</t>
+          <t>Biarritz</t>
         </is>
       </c>
       <c r="E164" s="15" t="n">
@@ -12349,7 +12357,7 @@
       </c>
       <c r="F164" s="15" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G164" s="15" t="inlineStr">
@@ -12371,7 +12379,7 @@
         <v>19</v>
       </c>
       <c r="K164" s="15" t="n">
-        <v>1.5</v>
+        <v>5.25</v>
       </c>
       <c r="L164" s="15" t="inlineStr"/>
       <c r="M164" s="15" t="inlineStr"/>
@@ -12388,12 +12396,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-18115</t>
+          <t>PDMDEP-18212</t>
         </is>
       </c>
       <c r="B165" s="12" t="inlineStr">
         <is>
-          <t>[Bischwiller] Migration + Pax + M2M</t>
+          <t>[Besancon] Acquisition</t>
         </is>
       </c>
       <c r="C165" s="12" t="inlineStr">
@@ -12403,7 +12411,7 @@
       </c>
       <c r="D165" s="12" t="inlineStr">
         <is>
-          <t>BISCHWILLER</t>
+          <t>Besançon</t>
         </is>
       </c>
       <c r="E165" s="12" t="n">
@@ -12416,39 +12424,31 @@
       </c>
       <c r="G165" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I165" s="12" t="inlineStr">
         <is>
-          <t>17/12/2024</t>
+          <t>20/12/2024</t>
         </is>
       </c>
       <c r="J165" s="12" t="n">
         <v>19</v>
       </c>
       <c r="K165" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L165" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28019</t>
-        </is>
-      </c>
-      <c r="M165" s="12" t="inlineStr">
-        <is>
-          <t>455151</t>
-        </is>
-      </c>
+        <v>1.5</v>
+      </c>
+      <c r="L165" s="12" t="inlineStr"/>
+      <c r="M165" s="12" t="inlineStr"/>
       <c r="N165" s="13" t="n">
-        <v>240</v>
-      </c>
-      <c r="O165" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O165" s="13" t="n">
         <v>0</v>
       </c>
       <c r="P165" s="13" t="n">
@@ -12458,22 +12458,22 @@
     <row r="166">
       <c r="A166" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-18038</t>
+          <t>PDMDEP-18115</t>
         </is>
       </c>
       <c r="B166" s="15" t="inlineStr">
         <is>
-          <t>[CD 38] Reprise de 1644 AP</t>
+          <t>[Bischwiller] Migration + Pax + M2M</t>
         </is>
       </c>
       <c r="C166" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D166" s="15" t="inlineStr">
         <is>
-          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
+          <t>BISCHWILLER</t>
         </is>
       </c>
       <c r="E166" s="15" t="n">
@@ -12481,7 +12481,7 @@
       </c>
       <c r="F166" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G166" s="15" t="inlineStr">
@@ -12491,34 +12491,34 @@
       </c>
       <c r="H166" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I166" s="15" t="inlineStr">
         <is>
-          <t>12/12/2024</t>
+          <t>17/12/2024</t>
         </is>
       </c>
       <c r="J166" s="15" t="n">
         <v>19</v>
       </c>
       <c r="K166" s="15" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="L166" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-34362</t>
+          <t>PDMDEP-28019</t>
         </is>
       </c>
       <c r="M166" s="15" t="inlineStr">
         <is>
-          <t>458057</t>
+          <t>455151</t>
         </is>
       </c>
       <c r="N166" s="16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O166" s="16" t="n">
+        <v>240</v>
+      </c>
+      <c r="O166" s="17" t="n">
         <v>0</v>
       </c>
       <c r="P166" s="16" t="n">
@@ -12543,7 +12543,7 @@
       </c>
       <c r="D167" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
+          <t>[CD38] - Crédit de modélisation (Transformation Reprise AP)</t>
         </is>
       </c>
       <c r="E167" s="12" t="n">
@@ -12577,7 +12577,7 @@
       </c>
       <c r="L167" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-28020</t>
+          <t>PDMDEP-34362</t>
         </is>
       </c>
       <c r="M167" s="12" t="inlineStr">
@@ -12598,22 +12598,22 @@
     <row r="168">
       <c r="A168" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-17117</t>
+          <t>PDMDEP-18038</t>
         </is>
       </c>
       <c r="B168" s="15" t="inlineStr">
         <is>
-          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
+          <t>[CD 38] Reprise de 1644 AP</t>
         </is>
       </c>
       <c r="C168" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D168" s="15" t="inlineStr">
         <is>
-          <t>NÎMES</t>
+          <t>CONSEIL DEPARTEMENTAL DE L'ISERE (CD 38)</t>
         </is>
       </c>
       <c r="E168" s="15" t="n">
@@ -12636,30 +12636,30 @@
       </c>
       <c r="I168" s="15" t="inlineStr">
         <is>
-          <t>14/10/2024</t>
+          <t>12/12/2024</t>
         </is>
       </c>
       <c r="J168" s="15" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K168" s="15" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="L168" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-28005</t>
+          <t>PDMDEP-28020</t>
         </is>
       </c>
       <c r="M168" s="15" t="inlineStr">
         <is>
-          <t>448204</t>
+          <t>458057</t>
         </is>
       </c>
       <c r="N168" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O168" s="16" t="n">
-        <v>1237</v>
+        <v>0</v>
       </c>
       <c r="P168" s="16" t="n">
         <v>0</v>
@@ -12668,22 +12668,22 @@
     <row r="169">
       <c r="A169" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-16868</t>
+          <t>PDMDEP-17117</t>
         </is>
       </c>
       <c r="B169" s="12" t="inlineStr">
         <is>
-          <t>[Limoges] migration placier</t>
+          <t>[NÎMES] 12,5 jours d'accompagnement client</t>
         </is>
       </c>
       <c r="C169" s="12" t="inlineStr">
         <is>
-          <t>Alizée MARGOT</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D169" s="12" t="inlineStr">
         <is>
-          <t>Limoges</t>
+          <t>NÎMES</t>
         </is>
       </c>
       <c r="E169" s="12" t="n">
@@ -12691,37 +12691,45 @@
       </c>
       <c r="F169" s="12" t="inlineStr">
         <is>
-          <t>GEODP</t>
+          <t>LITTERALIS</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Rework</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Migration</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I169" s="12" t="inlineStr">
         <is>
-          <t>26/09/2024</t>
+          <t>14/10/2024</t>
         </is>
       </c>
       <c r="J169" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K169" s="12" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="L169" s="12" t="inlineStr"/>
-      <c r="M169" s="12" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L169" s="12" t="inlineStr">
+        <is>
+          <t>PDMDEP-28005</t>
+        </is>
+      </c>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>448204</t>
+        </is>
+      </c>
       <c r="N169" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O169" s="13" t="n">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="P169" s="13" t="n">
         <v>0</v>
@@ -12730,22 +12738,22 @@
     <row r="170">
       <c r="A170" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-15695</t>
+          <t>PDMDEP-16868</t>
         </is>
       </c>
       <c r="B170" s="15" t="inlineStr">
         <is>
-          <t>[CD50 - MANCHE] Interface Pastell</t>
+          <t>[Limoges] migration placier</t>
         </is>
       </c>
       <c r="C170" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Alizée MARGOT</t>
         </is>
       </c>
       <c r="D170" s="15" t="inlineStr">
         <is>
-          <t>CD Manche</t>
+          <t>Limoges</t>
         </is>
       </c>
       <c r="E170" s="15" t="n">
@@ -12753,7 +12761,7 @@
       </c>
       <c r="F170" s="15" t="inlineStr">
         <is>
-          <t>LITTERALIS</t>
+          <t>GEODP</t>
         </is>
       </c>
       <c r="G170" s="15" t="inlineStr">
@@ -12763,19 +12771,19 @@
       </c>
       <c r="H170" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Migration</t>
         </is>
       </c>
       <c r="I170" s="15" t="inlineStr">
         <is>
-          <t>17/06/2024</t>
+          <t>26/09/2024</t>
         </is>
       </c>
       <c r="J170" s="15" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="K170" s="15" t="n">
-        <v>0.25</v>
+        <v>4.75</v>
       </c>
       <c r="L170" s="15" t="inlineStr"/>
       <c r="M170" s="15" t="inlineStr"/>
@@ -12792,22 +12800,22 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14798</t>
+          <t>PDMDEP-15695</t>
         </is>
       </c>
       <c r="B171" s="12" t="inlineStr">
         <is>
-          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
+          <t>[CD50 - MANCHE] Interface Pastell</t>
         </is>
       </c>
       <c r="C171" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D171" s="12" t="inlineStr">
         <is>
-          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
+          <t>CD Manche</t>
         </is>
       </c>
       <c r="E171" s="12" t="n">
@@ -12830,25 +12838,17 @@
       </c>
       <c r="I171" s="12" t="inlineStr">
         <is>
-          <t>05/04/2024</t>
+          <t>17/06/2024</t>
         </is>
       </c>
       <c r="J171" s="12" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="K171" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L171" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-28003</t>
-        </is>
-      </c>
-      <c r="M171" s="12" t="inlineStr">
-        <is>
-          <t>412981</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L171" s="12" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr"/>
       <c r="N171" s="13" t="n">
         <v>0</v>
       </c>
@@ -12862,12 +12862,12 @@
     <row r="172">
       <c r="A172" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14551</t>
+          <t>PDMDEP-14798</t>
         </is>
       </c>
       <c r="B172" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan] Interface formulaire</t>
+          <t>[CD 92 Hauts-de-Seine] Crédit 5j de param</t>
         </is>
       </c>
       <c r="C172" s="15" t="inlineStr">
@@ -12877,7 +12877,7 @@
       </c>
       <c r="D172" s="15" t="inlineStr">
         <is>
-          <t>[Perpignan]</t>
+          <t>CONSEIL DEPARTEMENTAL DES HAUTS DE SEINE (CD 92)</t>
         </is>
       </c>
       <c r="E172" s="15" t="n">
@@ -12900,17 +12900,25 @@
       </c>
       <c r="I172" s="15" t="inlineStr">
         <is>
-          <t>14/03/2024</t>
+          <t>05/04/2024</t>
         </is>
       </c>
       <c r="J172" s="15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="K172" s="15" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="L172" s="15" t="inlineStr"/>
-      <c r="M172" s="15" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="L172" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-28003</t>
+        </is>
+      </c>
+      <c r="M172" s="15" t="inlineStr">
+        <is>
+          <t>412981</t>
+        </is>
+      </c>
       <c r="N172" s="16" t="n">
         <v>0</v>
       </c>
@@ -12924,22 +12932,22 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14273</t>
+          <t>PDMDEP-14551</t>
         </is>
       </c>
       <c r="B173" s="12" t="inlineStr">
         <is>
-          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
+          <t>[Perpignan] Interface formulaire</t>
         </is>
       </c>
       <c r="C173" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D173" s="12" t="inlineStr">
         <is>
-          <t>CD Marne</t>
+          <t>[Perpignan]</t>
         </is>
       </c>
       <c r="E173" s="12" t="n">
@@ -12962,14 +12970,14 @@
       </c>
       <c r="I173" s="12" t="inlineStr">
         <is>
-          <t>20/02/2024</t>
+          <t>14/03/2024</t>
         </is>
       </c>
       <c r="J173" s="12" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="K173" s="12" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L173" s="12" t="inlineStr"/>
       <c r="M173" s="12" t="inlineStr"/>
@@ -12986,22 +12994,22 @@
     <row r="174">
       <c r="A174" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-14254</t>
+          <t>PDMDEP-14273</t>
         </is>
       </c>
       <c r="B174" s="15" t="inlineStr">
         <is>
-          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
+          <t>[CD51 - MARNE] Modélisation, visa et Interface BG</t>
         </is>
       </c>
       <c r="C174" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D174" s="15" t="inlineStr">
         <is>
-          <t>Dijon métropole</t>
+          <t>CD Marne</t>
         </is>
       </c>
       <c r="E174" s="15" t="n">
@@ -13024,14 +13032,14 @@
       </c>
       <c r="I174" s="15" t="inlineStr">
         <is>
-          <t>19/02/2024</t>
+          <t>20/02/2024</t>
         </is>
       </c>
       <c r="J174" s="15" t="n">
         <v>29</v>
       </c>
       <c r="K174" s="15" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L174" s="15" t="inlineStr"/>
       <c r="M174" s="15" t="inlineStr"/>
@@ -13048,22 +13056,22 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-14095</t>
+          <t>PDMDEP-14254</t>
         </is>
       </c>
       <c r="B175" s="12" t="inlineStr">
         <is>
-          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
+          <t>[Dijon métropole] dev spécifique : gestion des anomalies</t>
         </is>
       </c>
       <c r="C175" s="12" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D175" s="12" t="inlineStr">
         <is>
-          <t>CC du Pays Sabolien</t>
+          <t>Dijon métropole</t>
         </is>
       </c>
       <c r="E175" s="12" t="n">
@@ -13081,19 +13089,19 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I175" s="12" t="inlineStr">
         <is>
-          <t>31/01/2024</t>
+          <t>19/02/2024</t>
         </is>
       </c>
       <c r="J175" s="12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K175" s="12" t="n">
-        <v>8</v>
+        <v>1.5</v>
       </c>
       <c r="L175" s="12" t="inlineStr"/>
       <c r="M175" s="12" t="inlineStr"/>
@@ -13110,22 +13118,22 @@
     <row r="176">
       <c r="A176" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-13488</t>
+          <t>PDMDEP-14095</t>
         </is>
       </c>
       <c r="B176" s="15" t="inlineStr">
         <is>
-          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
+          <t>[CC PAYS SABOLIEN] Littéralis Prime hebergé CC &amp; multivilles</t>
         </is>
       </c>
       <c r="C176" s="15" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D176" s="15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asnieres sur Seine </t>
+          <t>CC du Pays Sabolien</t>
         </is>
       </c>
       <c r="E176" s="15" t="n">
@@ -13143,19 +13151,19 @@
       </c>
       <c r="H176" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I176" s="15" t="inlineStr">
         <is>
-          <t>30/11/2023</t>
+          <t>31/01/2024</t>
         </is>
       </c>
       <c r="J176" s="15" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K176" s="15" t="n">
-        <v>0.25</v>
+        <v>8</v>
       </c>
       <c r="L176" s="15" t="inlineStr"/>
       <c r="M176" s="15" t="inlineStr"/>
@@ -13172,12 +13180,12 @@
     <row r="177">
       <c r="A177" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12747</t>
+          <t>PDMDEP-13488</t>
         </is>
       </c>
       <c r="B177" s="12" t="inlineStr">
         <is>
-          <t>[FOUGERES] ARPEGE</t>
+          <t>[Asnieres sur Seine] Civil Net + IXBUS + Hébergement</t>
         </is>
       </c>
       <c r="C177" s="12" t="inlineStr">
@@ -13187,7 +13195,7 @@
       </c>
       <c r="D177" s="12" t="inlineStr">
         <is>
-          <t>FOUGERES</t>
+          <t xml:space="preserve">Asnieres sur Seine </t>
         </is>
       </c>
       <c r="E177" s="12" t="n">
@@ -13200,7 +13208,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Rework</t>
         </is>
       </c>
       <c r="H177" s="12" t="inlineStr">
@@ -13210,25 +13218,17 @@
       </c>
       <c r="I177" s="12" t="inlineStr">
         <is>
-          <t>26/09/2023</t>
+          <t>30/11/2023</t>
         </is>
       </c>
       <c r="J177" s="12" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="K177" s="12" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="L177" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-27990</t>
-        </is>
-      </c>
-      <c r="M177" s="12" t="inlineStr">
-        <is>
-          <t>406296</t>
-        </is>
-      </c>
+        <v>0.25</v>
+      </c>
+      <c r="L177" s="12" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr"/>
       <c r="N177" s="13" t="n">
         <v>0</v>
       </c>
@@ -13242,22 +13242,22 @@
     <row r="178">
       <c r="A178" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12708</t>
+          <t>PDMDEP-12747</t>
         </is>
       </c>
       <c r="B178" s="15" t="inlineStr">
         <is>
-          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
+          <t>[FOUGERES] ARPEGE</t>
         </is>
       </c>
       <c r="C178" s="15" t="inlineStr">
         <is>
-          <t>Remy VINCENT</t>
+          <t>Fabien REUTENAUER</t>
         </is>
       </c>
       <c r="D178" s="15" t="inlineStr">
         <is>
-          <t>CD 56 MORBIHAN</t>
+          <t>FOUGERES</t>
         </is>
       </c>
       <c r="E178" s="15" t="n">
@@ -13270,23 +13270,35 @@
       </c>
       <c r="G178" s="15" t="inlineStr">
         <is>
-          <t>Rework</t>
-        </is>
-      </c>
-      <c r="H178" s="15" t="inlineStr"/>
+          <t>Projet</t>
+        </is>
+      </c>
+      <c r="H178" s="15" t="inlineStr">
+        <is>
+          <t>Vente additionnelle</t>
+        </is>
+      </c>
       <c r="I178" s="15" t="inlineStr">
         <is>
-          <t>22/09/2023</t>
+          <t>26/09/2023</t>
         </is>
       </c>
       <c r="J178" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K178" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L178" s="15" t="inlineStr"/>
-      <c r="M178" s="15" t="inlineStr"/>
+        <v>11.5</v>
+      </c>
+      <c r="L178" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-27990</t>
+        </is>
+      </c>
+      <c r="M178" s="15" t="inlineStr">
+        <is>
+          <t>406296</t>
+        </is>
+      </c>
       <c r="N178" s="16" t="n">
         <v>0</v>
       </c>
@@ -13300,12 +13312,12 @@
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12666</t>
+          <t>PDMDEP-12708</t>
         </is>
       </c>
       <c r="B179" s="12" t="inlineStr">
         <is>
-          <t>[LE MANS METROPOLE] Littéralis Expert</t>
+          <t>[CD56 - MORBIHAN] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C179" s="12" t="inlineStr">
@@ -13315,7 +13327,7 @@
       </c>
       <c r="D179" s="12" t="inlineStr">
         <is>
-          <t>LE MANS METROPOLE</t>
+          <t>CD 56 MORBIHAN</t>
         </is>
       </c>
       <c r="E179" s="12" t="n">
@@ -13331,32 +13343,20 @@
           <t>Rework</t>
         </is>
       </c>
-      <c r="H179" s="12" t="inlineStr">
-        <is>
-          <t>Nouveau déploiement</t>
-        </is>
-      </c>
+      <c r="H179" s="12" t="inlineStr"/>
       <c r="I179" s="12" t="inlineStr">
         <is>
-          <t>19/09/2023</t>
+          <t>22/09/2023</t>
         </is>
       </c>
       <c r="J179" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K179" s="12" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="L179" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34532</t>
-        </is>
-      </c>
-      <c r="M179" s="12" t="inlineStr">
-        <is>
-          <t>412263</t>
-        </is>
-      </c>
+        <v>0.5</v>
+      </c>
+      <c r="L179" s="12" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr"/>
       <c r="N179" s="13" t="n">
         <v>0</v>
       </c>
@@ -13370,12 +13370,12 @@
     <row r="180">
       <c r="A180" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12443</t>
+          <t>PDMDEP-12666</t>
         </is>
       </c>
       <c r="B180" s="15" t="inlineStr">
         <is>
-          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
+          <t>[LE MANS METROPOLE] Littéralis Expert</t>
         </is>
       </c>
       <c r="C180" s="15" t="inlineStr">
@@ -13385,7 +13385,7 @@
       </c>
       <c r="D180" s="15" t="inlineStr">
         <is>
-          <t>CD79 - Deux Sèvres</t>
+          <t>LE MANS METROPOLE</t>
         </is>
       </c>
       <c r="E180" s="15" t="n">
@@ -13408,17 +13408,25 @@
       </c>
       <c r="I180" s="15" t="inlineStr">
         <is>
-          <t>04/09/2023</t>
+          <t>19/09/2023</t>
         </is>
       </c>
       <c r="J180" s="15" t="n">
         <v>34</v>
       </c>
       <c r="K180" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="L180" s="15" t="inlineStr"/>
-      <c r="M180" s="15" t="inlineStr"/>
+        <v>2.75</v>
+      </c>
+      <c r="L180" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-34532</t>
+        </is>
+      </c>
+      <c r="M180" s="15" t="inlineStr">
+        <is>
+          <t>412263</t>
+        </is>
+      </c>
       <c r="N180" s="16" t="n">
         <v>0</v>
       </c>
@@ -13432,28 +13440,26 @@
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-12241</t>
+          <t>PDMDEP-12443</t>
         </is>
       </c>
       <c r="B181" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
+          <t>[CD79 - LES DEUX SEVRES] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C181" s="12" t="inlineStr">
         <is>
-          <t>Fabien REUTENAUER</t>
+          <t>Remy VINCENT</t>
         </is>
       </c>
       <c r="D181" s="12" t="inlineStr">
         <is>
-          <t>[SM Routes de Guadeloupe]</t>
-        </is>
-      </c>
-      <c r="E181" s="12" t="inlineStr">
-        <is>
-          <t>Déploiement de Littéralis Expert</t>
-        </is>
+          <t>CD79 - Deux Sèvres</t>
+        </is>
+      </c>
+      <c r="E181" s="12" t="n">
+        <v/>
       </c>
       <c r="F181" s="12" t="inlineStr">
         <is>
@@ -13479,7 +13485,7 @@
         <v>34</v>
       </c>
       <c r="K181" s="12" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L181" s="12" t="inlineStr"/>
       <c r="M181" s="12" t="inlineStr"/>
@@ -13496,12 +13502,12 @@
     <row r="182">
       <c r="A182" s="14" t="inlineStr">
         <is>
-          <t>PDMDEP-12222</t>
+          <t>PDMDEP-12241</t>
         </is>
       </c>
       <c r="B182" s="15" t="inlineStr">
         <is>
-          <t>[CD 14] Paramétrages</t>
+          <t>[SM Routes de Guadeloupe] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C182" s="15" t="inlineStr">
@@ -13511,12 +13517,12 @@
       </c>
       <c r="D182" s="15" t="inlineStr">
         <is>
-          <t>CD14</t>
+          <t>[SM Routes de Guadeloupe]</t>
         </is>
       </c>
       <c r="E182" s="15" t="inlineStr">
         <is>
-          <t>Modélisation spécifique</t>
+          <t>Déploiement de Littéralis Expert</t>
         </is>
       </c>
       <c r="F182" s="15" t="inlineStr">
@@ -13531,7 +13537,7 @@
       </c>
       <c r="H182" s="15" t="inlineStr">
         <is>
-          <t>Vente additionnelle</t>
+          <t>Nouveau déploiement</t>
         </is>
       </c>
       <c r="I182" s="15" t="inlineStr">
@@ -13543,7 +13549,7 @@
         <v>34</v>
       </c>
       <c r="K182" s="15" t="n">
-        <v>9.5</v>
+        <v>0.5</v>
       </c>
       <c r="L182" s="15" t="inlineStr"/>
       <c r="M182" s="15" t="inlineStr"/>
@@ -13560,23 +13566,27 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t>PDMDEP-11477</t>
+          <t>PDMDEP-12222</t>
         </is>
       </c>
       <c r="B183" s="12" t="inlineStr">
         <is>
-          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
-        </is>
-      </c>
-      <c r="C183" s="12" t="inlineStr"/>
+          <t>[CD 14] Paramétrages</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>Fabien REUTENAUER</t>
+        </is>
+      </c>
       <c r="D183" s="12" t="inlineStr">
         <is>
-          <t>MONTPELLIER MMM</t>
+          <t>CD14</t>
         </is>
       </c>
       <c r="E183" s="12" t="inlineStr">
         <is>
-          <t>Déploiement Module AC</t>
+          <t>Modélisation spécifique</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
@@ -13591,19 +13601,19 @@
       </c>
       <c r="H183" s="12" t="inlineStr">
         <is>
-          <t>Nouveau déploiement</t>
+          <t>Vente additionnelle</t>
         </is>
       </c>
       <c r="I183" s="12" t="inlineStr">
         <is>
-          <t>03/09/2023</t>
+          <t>04/09/2023</t>
         </is>
       </c>
       <c r="J183" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K183" s="12" t="n">
-        <v>1.75</v>
+        <v>9.5</v>
       </c>
       <c r="L183" s="12" t="inlineStr"/>
       <c r="M183" s="12" t="inlineStr"/>
@@ -13620,21 +13630,25 @@
     <row r="184">
       <c r="A184" s="14" t="inlineStr">
         <is>
-          <t>PSC-1334</t>
+          <t>PDMDEP-11477</t>
         </is>
       </c>
       <c r="B184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
+          <t>[MONTPELLIER MMM - Module AC] LITTERALIS EXPERT</t>
         </is>
       </c>
       <c r="C184" s="15" t="inlineStr"/>
       <c r="D184" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MOUY</t>
-        </is>
-      </c>
-      <c r="E184" s="15" t="inlineStr"/>
+          <t>MONTPELLIER MMM</t>
+        </is>
+      </c>
+      <c r="E184" s="15" t="inlineStr">
+        <is>
+          <t>Déploiement Module AC</t>
+        </is>
+      </c>
       <c r="F184" s="15" t="inlineStr">
         <is>
           <t>LITTERALIS</t>
@@ -13642,20 +13656,24 @@
       </c>
       <c r="G184" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
-        </is>
-      </c>
-      <c r="H184" s="15" t="inlineStr"/>
+          <t>Rework</t>
+        </is>
+      </c>
+      <c r="H184" s="15" t="inlineStr">
+        <is>
+          <t>Nouveau déploiement</t>
+        </is>
+      </c>
       <c r="I184" s="15" t="inlineStr">
         <is>
-          <t>30/07/2026</t>
+          <t>03/09/2023</t>
         </is>
       </c>
       <c r="J184" s="15" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="K184" s="15" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="L184" s="15" t="inlineStr"/>
       <c r="M184" s="15" t="inlineStr"/>
@@ -13672,18 +13690,18 @@
     <row r="185">
       <c r="A185" s="11" t="inlineStr">
         <is>
-          <t>PSC-1326</t>
+          <t>PSC-1334</t>
         </is>
       </c>
       <c r="B185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="C185" s="12" t="inlineStr"/>
       <c r="D185" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE SAINT-ISMIER</t>
+          <t>MAIRIE DE MOUY</t>
         </is>
       </c>
       <c r="E185" s="12" t="inlineStr"/>
@@ -13700,7 +13718,7 @@
       <c r="H185" s="12" t="inlineStr"/>
       <c r="I185" s="12" t="inlineStr">
         <is>
-          <t>29/07/2026</t>
+          <t>30/07/2026</t>
         </is>
       </c>
       <c r="J185" s="12" t="n">
@@ -13724,18 +13742,18 @@
     <row r="186">
       <c r="A186" s="14" t="inlineStr">
         <is>
-          <t>PSC-1310</t>
+          <t>PSC-1326</t>
         </is>
       </c>
       <c r="B186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="C186" s="15" t="inlineStr"/>
       <c r="D186" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
+          <t>MAIRIE DE SAINT-ISMIER</t>
         </is>
       </c>
       <c r="E186" s="15" t="inlineStr"/>
@@ -13752,14 +13770,14 @@
       <c r="H186" s="15" t="inlineStr"/>
       <c r="I186" s="15" t="inlineStr">
         <is>
-          <t>29/06/2026</t>
+          <t>29/07/2026</t>
         </is>
       </c>
       <c r="J186" s="15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K186" s="15" t="n">
-        <v>0.75</v>
+        <v>0.25</v>
       </c>
       <c r="L186" s="15" t="inlineStr"/>
       <c r="M186" s="15" t="inlineStr"/>
@@ -13776,18 +13794,18 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t>PSC-1283</t>
+          <t>PSC-1310</t>
         </is>
       </c>
       <c r="B187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="C187" s="12" t="inlineStr"/>
       <c r="D187" s="12" t="inlineStr">
         <is>
-          <t>MAIRIE DE ANNET SUR MARNE</t>
+          <t>COMMUNE DE NOIRMOUTIER-EN-L'ILE</t>
         </is>
       </c>
       <c r="E187" s="12" t="inlineStr"/>
@@ -13798,36 +13816,28 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>Projet</t>
+          <t>Commande sans prestation</t>
         </is>
       </c>
       <c r="H187" s="12" t="inlineStr"/>
       <c r="I187" s="12" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="J187" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K187" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L187" s="12" t="inlineStr">
-        <is>
-          <t>PDMDEP-34335</t>
-        </is>
-      </c>
-      <c r="M187" s="12" t="inlineStr">
-        <is>
-          <t>00168072</t>
-        </is>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="L187" s="12" t="inlineStr"/>
+      <c r="M187" s="12" t="inlineStr"/>
       <c r="N187" s="13" t="n">
         <v>0</v>
       </c>
       <c r="O187" s="13" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="P187" s="13" t="n">
         <v>0</v>
@@ -13836,18 +13846,18 @@
     <row r="188">
       <c r="A188" s="14" t="inlineStr">
         <is>
-          <t>PSC-1270</t>
+          <t>PSC-1283</t>
         </is>
       </c>
       <c r="B188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="C188" s="15" t="inlineStr"/>
       <c r="D188" s="15" t="inlineStr">
         <is>
-          <t>COMMUNE DE CASTELNAUDARY</t>
+          <t>MAIRIE DE ANNET SUR MARNE</t>
         </is>
       </c>
       <c r="E188" s="15" t="inlineStr"/>
@@ -13864,50 +13874,50 @@
       <c r="H188" s="15" t="inlineStr"/>
       <c r="I188" s="15" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="J188" s="15" t="n">
         <v>2</v>
       </c>
       <c r="K188" s="15" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="L188" s="15" t="inlineStr">
         <is>
-          <t>PDMDEP-33362</t>
+          <t>PDMDEP-34335</t>
         </is>
       </c>
       <c r="M188" s="15" t="inlineStr">
         <is>
-          <t>00167140</t>
+          <t>00168072</t>
         </is>
       </c>
       <c r="N188" s="16" t="n">
-        <v>510.6</v>
+        <v>0</v>
       </c>
       <c r="O188" s="16" t="n">
-        <v>680.8</v>
+        <v>150</v>
       </c>
       <c r="P188" s="16" t="n">
-        <v>247.56</v>
+        <v>0</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t>PSC-1240</t>
+          <t>PSC-1270</t>
         </is>
       </c>
       <c r="B189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="C189" s="12" t="inlineStr"/>
       <c r="D189" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE BRANNE</t>
+          <t>COMMUNE DE CASTELNAUDARY</t>
         </is>
       </c>
       <c r="E189" s="12" t="inlineStr"/>
@@ -13924,50 +13934,50 @@
       <c r="H189" s="12" t="inlineStr"/>
       <c r="I189" s="12" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="J189" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K189" s="12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="L189" s="12" t="inlineStr">
         <is>
-          <t>PDMDEP-33167</t>
+          <t>PDMDEP-33362</t>
         </is>
       </c>
       <c r="M189" s="12" t="inlineStr">
         <is>
-          <t>00165437</t>
+          <t>00167140</t>
         </is>
       </c>
       <c r="N189" s="13" t="n">
-        <v>0</v>
+        <v>510.6</v>
       </c>
       <c r="O189" s="13" t="n">
-        <v>100</v>
+        <v>680.8</v>
       </c>
       <c r="P189" s="13" t="n">
-        <v>0</v>
+        <v>247.56</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="14" t="inlineStr">
         <is>
-          <t>PSC-1182</t>
+          <t>PSC-1240</t>
         </is>
       </c>
       <c r="B190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="C190" s="15" t="inlineStr"/>
       <c r="D190" s="15" t="inlineStr">
         <is>
-          <t>Commune de La Ville aux Dames</t>
+          <t>COMMUNE DE BRANNE</t>
         </is>
       </c>
       <c r="E190" s="15" t="inlineStr"/>
@@ -13978,28 +13988,36 @@
       </c>
       <c r="G190" s="15" t="inlineStr">
         <is>
-          <t>Commande sans prestation</t>
+          <t>Projet</t>
         </is>
       </c>
       <c r="H190" s="15" t="inlineStr"/>
       <c r="I190" s="15" t="inlineStr">
         <is>
-          <t>10/03/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="J190" s="15" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K190" s="15" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="L190" s="15" t="inlineStr"/>
-      <c r="M190" s="15" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="L190" s="15" t="inlineStr">
+        <is>
+          <t>PDMDEP-33167</t>
+        </is>
+      </c>
+      <c r="M190" s="15" t="inlineStr">
+        <is>
+          <t>00165437</t>
+        </is>
+      </c>
       <c r="N190" s="16" t="n">
         <v>0</v>
       </c>
       <c r="O190" s="16" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="P190" s="16" t="n">
         <v>0</v>
@@ -14008,18 +14026,18 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t>PSC-1126</t>
+          <t>PSC-1182</t>
         </is>
       </c>
       <c r="B191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr"/>
       <c r="D191" s="12" t="inlineStr">
         <is>
-          <t>COMMUNE DE CARRY LE ROUET</t>
+          <t>Commune de La Ville aux Dames</t>
         </is>
       </c>
       <c r="E191" s="12" t="inlineStr"/>
@@ -14036,14 +14054,14 @@
       <c r="H191" s="12" t="inlineStr"/>
       <c r="I191" s="12" t="inlineStr">
         <is>
-          <t>26/01/2026</t>
+          <t>10/03/2026</t>
         </is>
       </c>
       <c r="J191" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K191" s="12" t="n">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="L191" s="12" t="inlineStr"/>
       <c r="M191" s="12" t="inlineStr"/>
@@ -14060,18 +14078,18 @@
     <row r="192">
       <c r="A192" s="14" t="inlineStr">
         <is>
-          <t>PSC-1021</t>
+          <t>PSC-1126</t>
         </is>
       </c>
       <c r="B192" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="C192" s="15" t="inlineStr"/>
       <c r="D192" s="15" t="inlineStr">
         <is>
-          <t>MAIRIE DE MELESSE</t>
+          <t>COMMUNE DE CARRY LE ROUET</t>
         </is>
       </c>
       <c r="E192" s="15" t="inlineStr"/>
@@ -14088,14 +14106,14 @@
       <c r="H192" s="15" t="inlineStr"/>
       <c r="I192" s="15" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>26/01/2026</t>
         </is>
       </c>
       <c r="J192" s="15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="K192" s="15" t="n">
-        <v>0.5</v>
+        <v>0.25</v>
       </c>
       <c r="L192" s="15" t="inlineStr"/>
       <c r="M192" s="15" t="inlineStr"/>
@@ -14112,18 +14130,18 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t>PSC-589</t>
+          <t>PSC-1021</t>
         </is>
       </c>
       <c r="B193" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="C193" s="12" t="inlineStr"/>
       <c r="D193" s="12" t="inlineStr">
         <is>
-          <t>Mairie de Venelles</t>
+          <t>MAIRIE DE MELESSE</t>
         </is>
       </c>
       <c r="E193" s="12" t="inlineStr"/>
@@ -14140,11 +14158,11 @@
       <c r="H193" s="12" t="inlineStr"/>
       <c r="I193" s="12" t="inlineStr">
         <is>
-          <t>20/03/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="J193" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K193" s="12" t="n">
         <v>0.5</v>
@@ -14162,31 +14180,83 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="18" t="inlineStr">
+      <c r="A194" s="14" t="inlineStr">
+        <is>
+          <t>PSC-589</t>
+        </is>
+      </c>
+      <c r="B194" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="C194" s="15" t="inlineStr"/>
+      <c r="D194" s="15" t="inlineStr">
+        <is>
+          <t>Mairie de Venelles</t>
+        </is>
+      </c>
+      <c r="E194" s="15" t="inlineStr"/>
+      <c r="F194" s="15" t="inlineStr">
+        <is>
+          <t>LITTERALIS</t>
+        </is>
+      </c>
+      <c r="G194" s="15" t="inlineStr">
+        <is>
+          <t>Commande sans prestation</t>
+        </is>
+      </c>
+      <c r="H194" s="15" t="inlineStr"/>
+      <c r="I194" s="15" t="inlineStr">
+        <is>
+          <t>20/03/2025</t>
+        </is>
+      </c>
+      <c r="J194" s="15" t="n">
+        <v>16</v>
+      </c>
+      <c r="K194" s="15" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="L194" s="15" t="inlineStr"/>
+      <c r="M194" s="15" t="inlineStr"/>
+      <c r="N194" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O194" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P194" s="16" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="18" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B194" s="18" t="inlineStr"/>
-      <c r="C194" s="18" t="inlineStr"/>
-      <c r="D194" s="18" t="inlineStr"/>
-      <c r="E194" s="18" t="inlineStr"/>
-      <c r="F194" s="18" t="inlineStr"/>
-      <c r="G194" s="18" t="inlineStr"/>
-      <c r="H194" s="18" t="inlineStr"/>
-      <c r="I194" s="18" t="inlineStr"/>
-      <c r="J194" s="18" t="inlineStr"/>
-      <c r="K194" s="18" t="inlineStr"/>
-      <c r="L194" s="18" t="inlineStr"/>
-      <c r="M194" s="18" t="inlineStr"/>
-      <c r="N194" s="19" t="n">
+      <c r="B195" s="18" t="inlineStr"/>
+      <c r="C195" s="18" t="inlineStr"/>
+      <c r="D195" s="18" t="inlineStr"/>
+      <c r="E195" s="18" t="inlineStr"/>
+      <c r="F195" s="18" t="inlineStr"/>
+      <c r="G195" s="18" t="inlineStr"/>
+      <c r="H195" s="18" t="inlineStr"/>
+      <c r="I195" s="18" t="inlineStr"/>
+      <c r="J195" s="18" t="inlineStr"/>
+      <c r="K195" s="18" t="inlineStr"/>
+      <c r="L195" s="18" t="inlineStr"/>
+      <c r="M195" s="18" t="inlineStr"/>
+      <c r="N195" s="19" t="n">
         <v>56423.7</v>
       </c>
-      <c r="O194" s="19" t="n">
-        <v>76299.079</v>
-      </c>
-      <c r="P194" s="19" t="n">
-        <v>200.65</v>
+      <c r="O195" s="19" t="n">
+        <v>77197.41899999999</v>
+      </c>
+      <c r="P195" s="19" t="n">
+        <v>203.01</v>
       </c>
     </row>
   </sheetData>
@@ -14381,6 +14451,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A191" r:id="rId187"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A192" r:id="rId188"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A193" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A194" r:id="rId190"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -15608,19 +15679,19 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>373553</v>
+        <v>372654</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>126750</v>
+        <v>126537</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>246803</v>
+        <v>246117</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>154731</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>22749</v>
+        <v>22063</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>26657</v>
@@ -15658,19 +15729,19 @@
         </is>
       </c>
       <c r="B7" s="27" t="n">
-        <v>199974</v>
+        <v>199076</v>
       </c>
       <c r="C7" s="27" t="n">
-        <v>60471</v>
+        <v>60259</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>139503</v>
+        <v>138817</v>
       </c>
       <c r="E7" s="27" t="n">
         <v>65928</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>10557</v>
+        <v>9871</v>
       </c>
       <c r="G7" s="27" t="n">
         <v>22953</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>78,016 €</t>
+          <t>78,901 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>82.1%</t>
+          <t>83.1%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>27,077 €</t>
+          <t>27,961 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -10193,10 +10193,10 @@
         <v>0</v>
       </c>
       <c r="O132" s="16" t="n">
-        <v>0</v>
+        <v>884.7</v>
       </c>
       <c r="P132" s="16" t="n">
-        <v>0</v>
+        <v>93.13</v>
       </c>
     </row>
     <row r="133">
@@ -14325,10 +14325,10 @@
         <v>55575</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>78016.36900000001</v>
+        <v>78901.069</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>205.17</v>
+        <v>207.49</v>
       </c>
     </row>
   </sheetData>
@@ -15752,19 +15752,19 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>371835</v>
+        <v>370951</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>126166</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>245670</v>
+        <v>244785</v>
       </c>
       <c r="E5" s="25" t="n">
         <v>154284</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>22063</v>
+        <v>21179</v>
       </c>
       <c r="G5" s="25" t="n">
         <v>26657</v>
@@ -15777,19 +15777,19 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>173579</v>
+        <v>172694</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>66279</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>107300</v>
+        <v>106415</v>
       </c>
       <c r="E6" s="26" t="n">
         <v>88803</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>12192</v>
+        <v>11307</v>
       </c>
       <c r="G6" s="26" t="n">
         <v>3705</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>78,901 €</t>
+          <t>80,116 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>83.1%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>27,961 €</t>
+          <t>29,176 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -11097,10 +11097,10 @@
         <v>0</v>
       </c>
       <c r="O145" s="13" t="n">
-        <v>126.2</v>
+        <v>378.609</v>
       </c>
       <c r="P145" s="13" t="n">
-        <v>63.1</v>
+        <v>189.3</v>
       </c>
     </row>
     <row r="146">
@@ -11723,10 +11723,10 @@
         <v>0</v>
       </c>
       <c r="O154" s="16" t="n">
-        <v>0</v>
+        <v>962.5</v>
       </c>
       <c r="P154" s="16" t="n">
-        <v>0</v>
+        <v>142.59</v>
       </c>
     </row>
     <row r="155">
@@ -14325,10 +14325,10 @@
         <v>55575</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>78901.069</v>
+        <v>80115.978</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>207.49</v>
+        <v>210.69</v>
       </c>
     </row>
   </sheetData>
@@ -15752,10 +15752,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>370951</v>
+        <v>369736</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>126166</v>
+        <v>124951</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>244785</v>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>172694</v>
+        <v>171479</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>66279</v>
+        <v>65064</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106415</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>80,116 €</t>
+          <t>80,391 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>84.3%</t>
+          <t>84.6%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,176 €</t>
+          <t>29,452 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -5193,7 +5193,7 @@
         <v>0</v>
       </c>
       <c r="O62" s="16" t="n">
-        <v>533.8049999999999</v>
+        <v>730.47</v>
       </c>
       <c r="P62" s="16" t="n">
         <v>0</v>
@@ -9211,7 +9211,7 @@
         <v>157.5</v>
       </c>
       <c r="O118" s="17" t="n">
-        <v>0</v>
+        <v>78.75</v>
       </c>
       <c r="P118" s="16" t="n">
         <v>0</v>
@@ -14325,10 +14325,10 @@
         <v>55575</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>80115.978</v>
+        <v>80391.393</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>210.69</v>
+        <v>211.41</v>
       </c>
     </row>
   </sheetData>
@@ -15752,22 +15752,22 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369736</v>
+        <v>369460</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>124951</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>244785</v>
+        <v>244509</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>154284</v>
+        <v>154205</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>26657</v>
+        <v>26461</v>
       </c>
     </row>
     <row r="6">
@@ -15777,22 +15777,22 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>171479</v>
+        <v>171204</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>65064</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106415</v>
+        <v>106140</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>88803</v>
+        <v>88724</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>11307</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>3705</v>
+        <v>3508</v>
       </c>
     </row>
     <row r="7">

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>80,391 €</t>
+          <t>80,476 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>84.6%</t>
+          <t>84.7%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,452 €</t>
+          <t>29,537 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -14029,10 +14029,10 @@
         <v>510.6</v>
       </c>
       <c r="O190" s="16" t="n">
-        <v>680.8</v>
+        <v>765.9</v>
       </c>
       <c r="P190" s="16" t="n">
-        <v>247.56</v>
+        <v>278.51</v>
       </c>
     </row>
     <row r="191">
@@ -14325,10 +14325,10 @@
         <v>55575</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>80391.393</v>
+        <v>80476.493</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>211.41</v>
+        <v>211.64</v>
       </c>
     </row>
   </sheetData>
@@ -15752,10 +15752,10 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369460</v>
+        <v>369375</v>
       </c>
       <c r="C5" s="25" t="n">
-        <v>124951</v>
+        <v>124866</v>
       </c>
       <c r="D5" s="25" t="n">
         <v>244509</v>
@@ -15777,10 +15777,10 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>171204</v>
+        <v>171119</v>
       </c>
       <c r="C6" s="26" t="n">
-        <v>65064</v>
+        <v>64979</v>
       </c>
       <c r="D6" s="26" t="n">
         <v>106140</v>

--- a/jira_export_2026-07-31.xlsx
+++ b/jira_export_2026-07-31.xlsx
@@ -732,7 +732,7 @@
     <row r="7" ht="26" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>80,476 €</t>
+          <t>82,891 €</t>
         </is>
       </c>
       <c r="B7" s="7" t="n"/>
@@ -746,7 +746,7 @@
       <c r="F7" s="7" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>84.7%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="H7" s="7" t="n"/>
@@ -772,7 +772,7 @@
     <row r="11" ht="26" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
-          <t>29,537 €</t>
+          <t>31,952 €</t>
         </is>
       </c>
       <c r="B11" s="7" t="n"/>
@@ -12801,7 +12801,7 @@
         <v>0</v>
       </c>
       <c r="O170" s="16" t="n">
-        <v>1237</v>
+        <v>3652</v>
       </c>
       <c r="P170" s="16" t="n">
         <v>0</v>
@@ -14325,10 +14325,10 @@
         <v>55575</v>
       </c>
       <c r="O196" s="19" t="n">
-        <v>80476.493</v>
+        <v>82891.493</v>
       </c>
       <c r="P196" s="19" t="n">
-        <v>211.64</v>
+        <v>217.99</v>
       </c>
     </row>
   </sheetData>
@@ -15752,16 +15752,16 @@
         </is>
       </c>
       <c r="B5" s="25" t="n">
-        <v>369375</v>
+        <v>366960</v>
       </c>
       <c r="C5" s="25" t="n">
         <v>124866</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>244509</v>
+        <v>242094</v>
       </c>
       <c r="E5" s="25" t="n">
-        <v>154205</v>
+        <v>151790</v>
       </c>
       <c r="F5" s="25" t="n">
         <v>21179</v>
@@ -15777,16 +15777,16 @@
         </is>
       </c>
       <c r="B6" s="26" t="n">
-        <v>171119</v>
+        <v>168704</v>
       </c>
       <c r="C6" s="26" t="n">
         <v>64979</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>106140</v>
+        <v>103725</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>88724</v>
+        <v>86309</v>
       </c>
       <c r="F6" s="26" t="n">
         <v>11307</v>
